--- a/testes/Financeiro/Planilhas_Base/MODELO.xlsx
+++ b/testes/Financeiro/Planilhas_Base/MODELO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\sistema_gestao_testes\testes\Financeiro\Planilhas_Base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\.shortcut-targets-by-id\195uuohIL_ZKum7lhwu-OzJCH_CGAb97G\Relatórios\Financeiro\Planilhas_Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8868BD88-84FD-4D69-B932-19E8CFC735F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3F0D630-06C9-4377-945F-415ED13EBDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13185" yWindow="15" windowWidth="15615" windowHeight="14910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="15285" windowHeight="14910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados" sheetId="3" r:id="rId1"/>
@@ -18,15 +18,15 @@
     <sheet name="Tp.Despesas" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dados!$A$1:$O$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dados!$A$1:$O$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">RESUMO!$A$1:$L$107</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Tp.Despesas!$A$1:$J$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">RESUMO!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">Tp.Despesas!$1:$5</definedName>
     <definedName name="Z_1F464119_5B8A_40C0_B182_993F69588B9D_.wvu.Cols" localSheetId="0" hidden="1">Dados!$H:$R</definedName>
-    <definedName name="Z_1F464119_5B8A_40C0_B182_993F69588B9D_.wvu.FilterData" localSheetId="0" hidden="1">Dados!$A$1:$O$2</definedName>
+    <definedName name="Z_1F464119_5B8A_40C0_B182_993F69588B9D_.wvu.FilterData" localSheetId="0" hidden="1">Dados!$A$1:$O$1</definedName>
     <definedName name="Z_4D7D1941_B5FD_47B6_8D54_2E45180B8868_.wvu.Cols" localSheetId="0" hidden="1">Dados!$H:$R</definedName>
-    <definedName name="Z_4D7D1941_B5FD_47B6_8D54_2E45180B8868_.wvu.FilterData" localSheetId="0" hidden="1">Dados!$A$1:$O$2</definedName>
+    <definedName name="Z_4D7D1941_B5FD_47B6_8D54_2E45180B8868_.wvu.FilterData" localSheetId="0" hidden="1">Dados!$A$1:$O$1</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,66 +41,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>emilia.mga@gmail.com</author>
-  </authors>
-  <commentList>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{878CDF7D-FE89-5845-BC50-02D972251041}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>emilia.mga@gmail.com:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">=C2&amp;D2&amp;E2&amp;G2&amp;J2&amp;K2
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{B2B3A3F0-F5E0-A34C-A444-25F325D0CD5D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>emilia.mga@gmail.com:</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>Rua  Zodiaco, 87  Sala 07 – Santa  Lúcia - Belo Horizonte - MG
 (31) 3654-6616 / (31) 99974-1241 /  (31) 98711-1139
@@ -194,12 +136,6 @@
     <t>ACUMULADO</t>
   </si>
   <si>
-    <t>CHECK</t>
-  </si>
-  <si>
-    <t>RELATÓRIO</t>
-  </si>
-  <si>
     <t>DATA_REL</t>
   </si>
   <si>
@@ -236,12 +172,6 @@
     <t>OBSERVAÇÃO</t>
   </si>
   <si>
-    <t>NF?</t>
-  </si>
-  <si>
-    <t>PAGTO</t>
-  </si>
-  <si>
     <t>[NOME]</t>
   </si>
   <si>
@@ -269,9 +199,9 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="[&lt;=99999999999]\ 000\.000\.000\-00;\ 00\.000\.000\/0000\-00"/>
     <numFmt numFmtId="169" formatCode="mm/yyyy"/>
-    <numFmt numFmtId="171" formatCode="#,##0_ ;\-#,##0\ "/>
+    <numFmt numFmtId="170" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -369,19 +299,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -403,7 +320,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -650,15 +567,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color theme="0" tint="-0.24994659260841701"/>
       </right>
@@ -702,7 +610,7 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -811,7 +719,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -823,27 +731,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -868,7 +774,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -878,6 +783,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -891,10 +800,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Hiperlink 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -907,7 +812,7 @@
     <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
     <cellStyle name="Vírgula 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -925,26 +830,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1353,130 +1238,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="51" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="49" customWidth="1"/>
     <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.5" style="52" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.5" style="42" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.875" style="42" customWidth="1"/>
-    <col min="7" max="7" width="12.5" style="66" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.625" style="53" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="56" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.875" style="54" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.375" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" style="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.5" style="50" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" style="40" customWidth="1"/>
+    <col min="7" max="7" width="12.5" style="57" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.625" style="51" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5" style="53" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.875" style="52" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.375" style="52" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="41.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.5" style="49" customWidth="1"/>
-    <col min="14" max="14" width="15" style="49" customWidth="1"/>
-    <col min="15" max="15" width="9.625" style="49" customWidth="1"/>
-    <col min="16" max="16" width="18.625" style="50" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.5" style="47" customWidth="1"/>
+    <col min="14" max="14" width="15" style="47" customWidth="1"/>
+    <col min="15" max="15" width="9.625" style="47" customWidth="1"/>
+    <col min="16" max="16" width="18.625" style="48" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.375" style="49" customWidth="1"/>
+    <col min="18" max="18" width="9.375" style="47" customWidth="1"/>
     <col min="19" max="16384" width="11.125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="D1" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="E1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="F1" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="H1" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="44" t="s">
+      <c r="I1" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="J1" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="K1" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="44" t="s">
+      <c r="L1" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="47" t="s">
+      <c r="M1" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="M1" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="N1" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="O1" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="P1" s="57" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q1" s="57" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41"/>
-      <c r="B2" s="55"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="H2"/>
-      <c r="J2" s="41"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2" s="40"/>
-      <c r="N2" t="str">
-        <f>IF(ISERROR(SEARCH("NF",E2,1)),"NÃO","SIM")</f>
-        <v>NÃO</v>
-      </c>
-      <c r="O2" t="str">
-        <f>IF($B2=5,"SIM","")</f>
-        <v/>
-      </c>
-      <c r="P2" s="50" t="str">
-        <f>A2&amp;B2&amp;C2&amp;E2&amp;G2&amp;EDATE(J2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1" t="str">
-        <f>IF(A2=0,"",VLOOKUP($A2,RESUMO!$A$8:$B$107,2,FALSE))</f>
-        <v/>
-      </c>
-    </row>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+    </row>
+    <row r="2" spans="1:17" ht="16.5" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:O2" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <conditionalFormatting sqref="O2:P2">
-    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
-      <formula>""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
+  <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <conditionalFormatting sqref="P2:P1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="17"/>
     <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1497,21 +1337,21 @@
     <row r="1" spans="1:20" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="G1" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
+      <c r="G1" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
     </row>
     <row r="2" spans="1:20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="2"/>
@@ -1522,15 +1362,15 @@
     </row>
     <row r="3" spans="1:20" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B3" s="5"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="K3" s="59" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" s="51"/>
+      <c r="K3" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" s="49"/>
       <c r="M3" s="5"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1538,15 +1378,15 @@
     </row>
     <row r="4" spans="1:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="K4" s="59" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" s="58"/>
+      <c r="K4" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="55"/>
       <c r="M4" s="3"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1619,35 +1459,35 @@
       </c>
     </row>
     <row r="9" spans="1:20" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="67">
-        <f>Dados!$A$3</f>
+      <c r="A9" s="58">
+        <f>Dados!$A$2</f>
         <v>0</v>
       </c>
       <c r="B9" s="24">
         <v>1</v>
       </c>
       <c r="C9" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A9)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A9)</f>
         <v>0</v>
       </c>
       <c r="D9" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A9)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A9)</f>
         <v>0</v>
       </c>
       <c r="E9" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A9)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A9)</f>
         <v>0</v>
       </c>
       <c r="F9" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A9)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A9)</f>
         <v>0</v>
       </c>
       <c r="G9" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A9)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A9)</f>
         <v>0</v>
       </c>
       <c r="H9" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A9)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A9)</f>
         <v>0</v>
       </c>
       <c r="I9" s="8">
@@ -1669,7 +1509,7 @@
       <c r="N9" s="35"/>
     </row>
     <row r="10" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="67">
+      <c r="A10" s="58">
         <f t="shared" ref="A10:A41" si="3">IF(DAY(A9)=20,DATE(YEAR(A9),MONTH(A9)+1,5),DATE(YEAR(A9),MONTH(A9),20))</f>
         <v>20</v>
       </c>
@@ -1678,27 +1518,27 @@
         <v>2</v>
       </c>
       <c r="C10" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A10)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A10)</f>
         <v>0</v>
       </c>
       <c r="D10" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A10)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A10)</f>
         <v>0</v>
       </c>
       <c r="E10" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A10)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A10)</f>
         <v>0</v>
       </c>
       <c r="F10" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A10)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A10)</f>
         <v>0</v>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A10)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A10)</f>
         <v>0</v>
       </c>
       <c r="H10" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A10)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A10)</f>
         <v>0</v>
       </c>
       <c r="I10" s="8">
@@ -1720,7 +1560,7 @@
       <c r="N10" s="35"/>
     </row>
     <row r="11" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="67">
+      <c r="A11" s="58">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
@@ -1729,27 +1569,27 @@
         <v>3</v>
       </c>
       <c r="C11" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A11)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A11)</f>
         <v>0</v>
       </c>
       <c r="D11" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A11)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A11)</f>
         <v>0</v>
       </c>
       <c r="E11" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A11)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A11)</f>
         <v>0</v>
       </c>
       <c r="F11" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A11)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A11)</f>
         <v>0</v>
       </c>
       <c r="G11" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A11)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A11)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A11)</f>
         <v>0</v>
       </c>
       <c r="I11" s="8">
@@ -1771,7 +1611,7 @@
       <c r="N11" s="35"/>
     </row>
     <row r="12" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="67">
+      <c r="A12" s="58">
         <f t="shared" si="3"/>
         <v>51</v>
       </c>
@@ -1780,27 +1620,27 @@
         <v>4</v>
       </c>
       <c r="C12" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A12)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A12)</f>
         <v>0</v>
       </c>
       <c r="D12" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A12)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A12)</f>
         <v>0</v>
       </c>
       <c r="E12" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A12)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A12)</f>
         <v>0</v>
       </c>
       <c r="F12" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A12)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A12)</f>
         <v>0</v>
       </c>
       <c r="G12" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A12)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A12)</f>
         <v>0</v>
       </c>
       <c r="H12" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A12)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A12)</f>
         <v>0</v>
       </c>
       <c r="I12" s="8">
@@ -1822,7 +1662,7 @@
       <c r="N12" s="35"/>
     </row>
     <row r="13" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="67">
+      <c r="A13" s="58">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
@@ -1831,27 +1671,27 @@
         <v>5</v>
       </c>
       <c r="C13" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A13)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A13)</f>
         <v>0</v>
       </c>
       <c r="D13" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A13)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A13)</f>
         <v>0</v>
       </c>
       <c r="E13" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A13)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A13)</f>
         <v>0</v>
       </c>
       <c r="F13" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A13)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A13)</f>
         <v>0</v>
       </c>
       <c r="G13" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A13)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A13)</f>
         <v>0</v>
       </c>
       <c r="H13" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A13)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A13)</f>
         <v>0</v>
       </c>
       <c r="I13" s="8">
@@ -1873,7 +1713,7 @@
       <c r="N13" s="35"/>
     </row>
     <row r="14" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="67">
+      <c r="A14" s="58">
         <f t="shared" si="3"/>
         <v>80</v>
       </c>
@@ -1882,27 +1722,27 @@
         <v>6</v>
       </c>
       <c r="C14" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A14)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A14)</f>
         <v>0</v>
       </c>
       <c r="D14" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A14)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A14)</f>
         <v>0</v>
       </c>
       <c r="E14" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A14)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A14)</f>
         <v>0</v>
       </c>
       <c r="F14" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A14)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A14)</f>
         <v>0</v>
       </c>
       <c r="G14" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A14)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A14)</f>
         <v>0</v>
       </c>
       <c r="H14" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A14)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A14)</f>
         <v>0</v>
       </c>
       <c r="I14" s="8">
@@ -1924,7 +1764,7 @@
       <c r="N14" s="35"/>
     </row>
     <row r="15" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="67">
+      <c r="A15" s="58">
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
@@ -1933,27 +1773,27 @@
         <v>7</v>
       </c>
       <c r="C15" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A15)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A15)</f>
         <v>0</v>
       </c>
       <c r="D15" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A15)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A15)</f>
         <v>0</v>
       </c>
       <c r="E15" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A15)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A15)</f>
         <v>0</v>
       </c>
       <c r="F15" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A15)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A15)</f>
         <v>0</v>
       </c>
       <c r="G15" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A15)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A15)</f>
         <v>0</v>
       </c>
       <c r="H15" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A15)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A15)</f>
         <v>0</v>
       </c>
       <c r="I15" s="8">
@@ -1975,7 +1815,7 @@
       <c r="N15" s="35"/>
     </row>
     <row r="16" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="67">
+      <c r="A16" s="58">
         <f t="shared" si="3"/>
         <v>111</v>
       </c>
@@ -1984,27 +1824,27 @@
         <v>8</v>
       </c>
       <c r="C16" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A16)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A16)</f>
         <v>0</v>
       </c>
       <c r="D16" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A16)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A16)</f>
         <v>0</v>
       </c>
       <c r="E16" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A16)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A16)</f>
         <v>0</v>
       </c>
       <c r="F16" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A16)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A16)</f>
         <v>0</v>
       </c>
       <c r="G16" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A16)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A16)</f>
         <v>0</v>
       </c>
       <c r="H16" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A16)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A16)</f>
         <v>0</v>
       </c>
       <c r="I16" s="8">
@@ -2026,7 +1866,7 @@
       <c r="N16" s="35"/>
     </row>
     <row r="17" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="67">
+      <c r="A17" s="58">
         <f t="shared" si="3"/>
         <v>126</v>
       </c>
@@ -2035,27 +1875,27 @@
         <v>9</v>
       </c>
       <c r="C17" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A17)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A17)</f>
         <v>0</v>
       </c>
       <c r="D17" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A17)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A17)</f>
         <v>0</v>
       </c>
       <c r="E17" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A17)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A17)</f>
         <v>0</v>
       </c>
       <c r="F17" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A17)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A17)</f>
         <v>0</v>
       </c>
       <c r="G17" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A17)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A17)</f>
         <v>0</v>
       </c>
       <c r="H17" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A17)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A17)</f>
         <v>0</v>
       </c>
       <c r="I17" s="8">
@@ -2077,7 +1917,7 @@
       <c r="N17" s="35"/>
     </row>
     <row r="18" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="67">
+      <c r="A18" s="58">
         <f t="shared" si="3"/>
         <v>141</v>
       </c>
@@ -2086,27 +1926,27 @@
         <v>10</v>
       </c>
       <c r="C18" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A18)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A18)</f>
         <v>0</v>
       </c>
       <c r="D18" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A18)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A18)</f>
         <v>0</v>
       </c>
       <c r="E18" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A18)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A18)</f>
         <v>0</v>
       </c>
       <c r="F18" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A18)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A18)</f>
         <v>0</v>
       </c>
       <c r="G18" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A18)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A18)</f>
         <v>0</v>
       </c>
       <c r="H18" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A18)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A18)</f>
         <v>0</v>
       </c>
       <c r="I18" s="8">
@@ -2128,7 +1968,7 @@
       <c r="N18" s="35"/>
     </row>
     <row r="19" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="67">
+      <c r="A19" s="58">
         <f t="shared" si="3"/>
         <v>157</v>
       </c>
@@ -2137,27 +1977,27 @@
         <v>11</v>
       </c>
       <c r="C19" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A19)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A19)</f>
         <v>0</v>
       </c>
       <c r="D19" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A19)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A19)</f>
         <v>0</v>
       </c>
       <c r="E19" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A19)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A19)</f>
         <v>0</v>
       </c>
       <c r="F19" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A19)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A19)</f>
         <v>0</v>
       </c>
       <c r="G19" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A19)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A19)</f>
         <v>0</v>
       </c>
       <c r="H19" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A19)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A19)</f>
         <v>0</v>
       </c>
       <c r="I19" s="8">
@@ -2179,7 +2019,7 @@
       <c r="N19" s="35"/>
     </row>
     <row r="20" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="67">
+      <c r="A20" s="58">
         <f t="shared" si="3"/>
         <v>172</v>
       </c>
@@ -2188,27 +2028,27 @@
         <v>12</v>
       </c>
       <c r="C20" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A20)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A20)</f>
         <v>0</v>
       </c>
       <c r="D20" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A20)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A20)</f>
         <v>0</v>
       </c>
       <c r="E20" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A20)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A20)</f>
         <v>0</v>
       </c>
       <c r="F20" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A20)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A20)</f>
         <v>0</v>
       </c>
       <c r="G20" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A20)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A20)</f>
         <v>0</v>
       </c>
       <c r="H20" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A20)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A20)</f>
         <v>0</v>
       </c>
       <c r="I20" s="8">
@@ -2230,7 +2070,7 @@
       <c r="N20" s="35"/>
     </row>
     <row r="21" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="67">
+      <c r="A21" s="58">
         <f t="shared" si="3"/>
         <v>187</v>
       </c>
@@ -2239,27 +2079,27 @@
         <v>13</v>
       </c>
       <c r="C21" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A21)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A21)</f>
         <v>0</v>
       </c>
       <c r="D21" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A21)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A21)</f>
         <v>0</v>
       </c>
       <c r="E21" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A21)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A21)</f>
         <v>0</v>
       </c>
       <c r="F21" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A21)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A21)</f>
         <v>0</v>
       </c>
       <c r="G21" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A21)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A21)</f>
         <v>0</v>
       </c>
       <c r="H21" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A21)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A21)</f>
         <v>0</v>
       </c>
       <c r="I21" s="8">
@@ -2281,7 +2121,7 @@
       <c r="N21" s="35"/>
     </row>
     <row r="22" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="67">
+      <c r="A22" s="58">
         <f t="shared" si="3"/>
         <v>202</v>
       </c>
@@ -2290,27 +2130,27 @@
         <v>14</v>
       </c>
       <c r="C22" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A22)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A22)</f>
         <v>0</v>
       </c>
       <c r="D22" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A22)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A22)</f>
         <v>0</v>
       </c>
       <c r="E22" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A22)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A22)</f>
         <v>0</v>
       </c>
       <c r="F22" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A22)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A22)</f>
         <v>0</v>
       </c>
       <c r="G22" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A22)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A22)</f>
         <v>0</v>
       </c>
       <c r="H22" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A22)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A22)</f>
         <v>0</v>
       </c>
       <c r="I22" s="8">
@@ -2332,7 +2172,7 @@
       <c r="N22" s="35"/>
     </row>
     <row r="23" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67">
+      <c r="A23" s="58">
         <f t="shared" si="3"/>
         <v>218</v>
       </c>
@@ -2341,27 +2181,27 @@
         <v>15</v>
       </c>
       <c r="C23" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A23)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A23)</f>
         <v>0</v>
       </c>
       <c r="D23" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A23)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A23)</f>
         <v>0</v>
       </c>
       <c r="E23" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A23)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A23)</f>
         <v>0</v>
       </c>
       <c r="F23" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A23)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A23)</f>
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A23)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A23)</f>
         <v>0</v>
       </c>
       <c r="H23" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A23)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A23)</f>
         <v>0</v>
       </c>
       <c r="I23" s="8">
@@ -2383,7 +2223,7 @@
       <c r="N23" s="35"/>
     </row>
     <row r="24" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="67">
+      <c r="A24" s="58">
         <f t="shared" si="3"/>
         <v>233</v>
       </c>
@@ -2392,27 +2232,27 @@
         <v>16</v>
       </c>
       <c r="C24" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A24)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A24)</f>
         <v>0</v>
       </c>
       <c r="D24" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A24)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A24)</f>
         <v>0</v>
       </c>
       <c r="E24" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A24)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A24)</f>
         <v>0</v>
       </c>
       <c r="F24" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A24)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A24)</f>
         <v>0</v>
       </c>
       <c r="G24" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A24)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A24)</f>
         <v>0</v>
       </c>
       <c r="H24" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A24)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A24)</f>
         <v>0</v>
       </c>
       <c r="I24" s="8">
@@ -2434,7 +2274,7 @@
       <c r="N24" s="35"/>
     </row>
     <row r="25" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="67">
+      <c r="A25" s="58">
         <f t="shared" si="3"/>
         <v>249</v>
       </c>
@@ -2443,27 +2283,27 @@
         <v>17</v>
       </c>
       <c r="C25" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A25)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A25)</f>
         <v>0</v>
       </c>
       <c r="D25" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A25)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A25)</f>
         <v>0</v>
       </c>
       <c r="E25" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A25)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A25)</f>
         <v>0</v>
       </c>
       <c r="F25" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A25)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A25)</f>
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A25)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A25)</f>
         <v>0</v>
       </c>
       <c r="H25" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A25)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A25)</f>
         <v>0</v>
       </c>
       <c r="I25" s="8">
@@ -2485,7 +2325,7 @@
       <c r="N25" s="35"/>
     </row>
     <row r="26" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="67">
+      <c r="A26" s="58">
         <f t="shared" si="3"/>
         <v>264</v>
       </c>
@@ -2494,27 +2334,27 @@
         <v>18</v>
       </c>
       <c r="C26" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A26)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A26)</f>
         <v>0</v>
       </c>
       <c r="D26" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A26)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A26)</f>
         <v>0</v>
       </c>
       <c r="E26" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A26)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A26)</f>
         <v>0</v>
       </c>
       <c r="F26" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A26)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A26)</f>
         <v>0</v>
       </c>
       <c r="G26" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A26)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A26)</f>
         <v>0</v>
       </c>
       <c r="H26" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A26)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A26)</f>
         <v>0</v>
       </c>
       <c r="I26" s="8">
@@ -2536,7 +2376,7 @@
       <c r="N26" s="35"/>
     </row>
     <row r="27" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="67">
+      <c r="A27" s="58">
         <f t="shared" si="3"/>
         <v>279</v>
       </c>
@@ -2545,27 +2385,27 @@
         <v>19</v>
       </c>
       <c r="C27" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A27)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A27)</f>
         <v>0</v>
       </c>
       <c r="D27" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A27)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A27)</f>
         <v>0</v>
       </c>
       <c r="E27" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A27)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A27)</f>
         <v>0</v>
       </c>
       <c r="F27" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A27)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A27)</f>
         <v>0</v>
       </c>
       <c r="G27" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A27)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A27)</f>
         <v>0</v>
       </c>
       <c r="H27" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A27)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A27)</f>
         <v>0</v>
       </c>
       <c r="I27" s="8">
@@ -2587,7 +2427,7 @@
       <c r="N27" s="35"/>
     </row>
     <row r="28" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="67">
+      <c r="A28" s="58">
         <f t="shared" si="3"/>
         <v>294</v>
       </c>
@@ -2596,27 +2436,27 @@
         <v>20</v>
       </c>
       <c r="C28" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A28)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A28)</f>
         <v>0</v>
       </c>
       <c r="D28" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A28)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A28)</f>
         <v>0</v>
       </c>
       <c r="E28" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A28)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A28)</f>
         <v>0</v>
       </c>
       <c r="F28" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A28)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A28)</f>
         <v>0</v>
       </c>
       <c r="G28" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A28)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A28)</f>
         <v>0</v>
       </c>
       <c r="H28" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A28)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A28)</f>
         <v>0</v>
       </c>
       <c r="I28" s="8">
@@ -2638,7 +2478,7 @@
       <c r="N28" s="35"/>
     </row>
     <row r="29" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="67">
+      <c r="A29" s="58">
         <f t="shared" si="3"/>
         <v>310</v>
       </c>
@@ -2647,27 +2487,27 @@
         <v>21</v>
       </c>
       <c r="C29" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A29)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A29)</f>
         <v>0</v>
       </c>
       <c r="D29" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A29)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A29)</f>
         <v>0</v>
       </c>
       <c r="E29" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A29)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A29)</f>
         <v>0</v>
       </c>
       <c r="F29" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A29)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A29)</f>
         <v>0</v>
       </c>
       <c r="G29" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A29)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A29)</f>
         <v>0</v>
       </c>
       <c r="H29" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A29)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A29)</f>
         <v>0</v>
       </c>
       <c r="I29" s="8">
@@ -2689,7 +2529,7 @@
       <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="67">
+      <c r="A30" s="58">
         <f t="shared" si="3"/>
         <v>325</v>
       </c>
@@ -2698,27 +2538,27 @@
         <v>22</v>
       </c>
       <c r="C30" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A30)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A30)</f>
         <v>0</v>
       </c>
       <c r="D30" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A30)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A30)</f>
         <v>0</v>
       </c>
       <c r="E30" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A30)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A30)</f>
         <v>0</v>
       </c>
       <c r="F30" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A30)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A30)</f>
         <v>0</v>
       </c>
       <c r="G30" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A30)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A30)</f>
         <v>0</v>
       </c>
       <c r="H30" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A30)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A30)</f>
         <v>0</v>
       </c>
       <c r="I30" s="8">
@@ -2740,7 +2580,7 @@
       <c r="N30" s="35"/>
     </row>
     <row r="31" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="67">
+      <c r="A31" s="58">
         <f t="shared" si="3"/>
         <v>340</v>
       </c>
@@ -2749,27 +2589,27 @@
         <v>23</v>
       </c>
       <c r="C31" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A31)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A31)</f>
         <v>0</v>
       </c>
       <c r="D31" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A31)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A31)</f>
         <v>0</v>
       </c>
       <c r="E31" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A31)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A31)</f>
         <v>0</v>
       </c>
       <c r="F31" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A31)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A31)</f>
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A31)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A31)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A31)</f>
         <v>0</v>
       </c>
       <c r="I31" s="8">
@@ -2791,7 +2631,7 @@
       <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="67">
+      <c r="A32" s="58">
         <f t="shared" si="3"/>
         <v>355</v>
       </c>
@@ -2800,27 +2640,27 @@
         <v>24</v>
       </c>
       <c r="C32" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A32)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A32)</f>
         <v>0</v>
       </c>
       <c r="D32" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A32)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A32)</f>
         <v>0</v>
       </c>
       <c r="E32" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A32)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A32)</f>
         <v>0</v>
       </c>
       <c r="F32" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A32)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A32)</f>
         <v>0</v>
       </c>
       <c r="G32" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A32)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A32)</f>
         <v>0</v>
       </c>
       <c r="H32" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A32)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A32)</f>
         <v>0</v>
       </c>
       <c r="I32" s="8">
@@ -2842,7 +2682,7 @@
       <c r="N32" s="35"/>
     </row>
     <row r="33" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="67">
+      <c r="A33" s="58">
         <f t="shared" si="3"/>
         <v>371</v>
       </c>
@@ -2851,27 +2691,27 @@
         <v>25</v>
       </c>
       <c r="C33" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A33)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A33)</f>
         <v>0</v>
       </c>
       <c r="D33" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A33)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A33)</f>
         <v>0</v>
       </c>
       <c r="E33" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A33)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A33)</f>
         <v>0</v>
       </c>
       <c r="F33" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A33)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A33)</f>
         <v>0</v>
       </c>
       <c r="G33" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A33)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A33)</f>
         <v>0</v>
       </c>
       <c r="H33" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A33)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A33)</f>
         <v>0</v>
       </c>
       <c r="I33" s="8">
@@ -2893,7 +2733,7 @@
       <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="67">
+      <c r="A34" s="58">
         <f t="shared" si="3"/>
         <v>386</v>
       </c>
@@ -2902,27 +2742,27 @@
         <v>26</v>
       </c>
       <c r="C34" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A34)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A34)</f>
         <v>0</v>
       </c>
       <c r="D34" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A34)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A34)</f>
         <v>0</v>
       </c>
       <c r="E34" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A34)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A34)</f>
         <v>0</v>
       </c>
       <c r="F34" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A34)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A34)</f>
         <v>0</v>
       </c>
       <c r="G34" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A34)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A34)</f>
         <v>0</v>
       </c>
       <c r="H34" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A34)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A34)</f>
         <v>0</v>
       </c>
       <c r="I34" s="8">
@@ -2944,7 +2784,7 @@
       <c r="N34" s="35"/>
     </row>
     <row r="35" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="67">
+      <c r="A35" s="58">
         <f t="shared" si="3"/>
         <v>402</v>
       </c>
@@ -2953,27 +2793,27 @@
         <v>27</v>
       </c>
       <c r="C35" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A35)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A35)</f>
         <v>0</v>
       </c>
       <c r="D35" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A35)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A35)</f>
         <v>0</v>
       </c>
       <c r="E35" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A35)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A35)</f>
         <v>0</v>
       </c>
       <c r="F35" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A35)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A35)</f>
         <v>0</v>
       </c>
       <c r="G35" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A35)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A35)</f>
         <v>0</v>
       </c>
       <c r="H35" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A35)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A35)</f>
         <v>0</v>
       </c>
       <c r="I35" s="8">
@@ -2995,7 +2835,7 @@
       <c r="N35" s="35"/>
     </row>
     <row r="36" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="67">
+      <c r="A36" s="58">
         <f t="shared" si="3"/>
         <v>417</v>
       </c>
@@ -3004,27 +2844,27 @@
         <v>28</v>
       </c>
       <c r="C36" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A36)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A36)</f>
         <v>0</v>
       </c>
       <c r="D36" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A36)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A36)</f>
         <v>0</v>
       </c>
       <c r="E36" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A36)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A36)</f>
         <v>0</v>
       </c>
       <c r="F36" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A36)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A36)</f>
         <v>0</v>
       </c>
       <c r="G36" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A36)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A36)</f>
         <v>0</v>
       </c>
       <c r="H36" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A36)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A36)</f>
         <v>0</v>
       </c>
       <c r="I36" s="8">
@@ -3046,7 +2886,7 @@
       <c r="N36" s="35"/>
     </row>
     <row r="37" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="67">
+      <c r="A37" s="58">
         <f t="shared" si="3"/>
         <v>430</v>
       </c>
@@ -3055,27 +2895,27 @@
         <v>29</v>
       </c>
       <c r="C37" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A37)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A37)</f>
         <v>0</v>
       </c>
       <c r="D37" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A37)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A37)</f>
         <v>0</v>
       </c>
       <c r="E37" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A37)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A37)</f>
         <v>0</v>
       </c>
       <c r="F37" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A37)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A37)</f>
         <v>0</v>
       </c>
       <c r="G37" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A37)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A37)</f>
         <v>0</v>
       </c>
       <c r="H37" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A37)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A37)</f>
         <v>0</v>
       </c>
       <c r="I37" s="8">
@@ -3097,7 +2937,7 @@
       <c r="N37" s="35"/>
     </row>
     <row r="38" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="67">
+      <c r="A38" s="58">
         <f t="shared" si="3"/>
         <v>445</v>
       </c>
@@ -3106,27 +2946,27 @@
         <v>30</v>
       </c>
       <c r="C38" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A38)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A38)</f>
         <v>0</v>
       </c>
       <c r="D38" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A38)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A38)</f>
         <v>0</v>
       </c>
       <c r="E38" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A38)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A38)</f>
         <v>0</v>
       </c>
       <c r="F38" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A38)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A38)</f>
         <v>0</v>
       </c>
       <c r="G38" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A38)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A38)</f>
         <v>0</v>
       </c>
       <c r="H38" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A38)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A38)</f>
         <v>0</v>
       </c>
       <c r="I38" s="8">
@@ -3148,7 +2988,7 @@
       <c r="N38" s="35"/>
     </row>
     <row r="39" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="67">
+      <c r="A39" s="58">
         <f t="shared" si="3"/>
         <v>461</v>
       </c>
@@ -3157,27 +2997,27 @@
         <v>31</v>
       </c>
       <c r="C39" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A39)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A39)</f>
         <v>0</v>
       </c>
       <c r="D39" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A39)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A39)</f>
         <v>0</v>
       </c>
       <c r="E39" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A39)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A39)</f>
         <v>0</v>
       </c>
       <c r="F39" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A39)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A39)</f>
         <v>0</v>
       </c>
       <c r="G39" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A39)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A39)</f>
         <v>0</v>
       </c>
       <c r="H39" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A39)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A39)</f>
         <v>0</v>
       </c>
       <c r="I39" s="8">
@@ -3199,7 +3039,7 @@
       <c r="N39" s="35"/>
     </row>
     <row r="40" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="67">
+      <c r="A40" s="58">
         <f t="shared" si="3"/>
         <v>476</v>
       </c>
@@ -3208,27 +3048,27 @@
         <v>32</v>
       </c>
       <c r="C40" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A40)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A40)</f>
         <v>0</v>
       </c>
       <c r="D40" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A40)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A40)</f>
         <v>0</v>
       </c>
       <c r="E40" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A40)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A40)</f>
         <v>0</v>
       </c>
       <c r="F40" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A40)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A40)</f>
         <v>0</v>
       </c>
       <c r="G40" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A40)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A40)</f>
         <v>0</v>
       </c>
       <c r="H40" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A40)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A40)</f>
         <v>0</v>
       </c>
       <c r="I40" s="8">
@@ -3250,7 +3090,7 @@
       <c r="N40" s="35"/>
     </row>
     <row r="41" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="67">
+      <c r="A41" s="58">
         <f t="shared" si="3"/>
         <v>491</v>
       </c>
@@ -3259,27 +3099,27 @@
         <v>33</v>
       </c>
       <c r="C41" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A41)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A41)</f>
         <v>0</v>
       </c>
       <c r="D41" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A41)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A41)</f>
         <v>0</v>
       </c>
       <c r="E41" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A41)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A41)</f>
         <v>0</v>
       </c>
       <c r="F41" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A41)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A41)</f>
         <v>0</v>
       </c>
       <c r="G41" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A41)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A41)</f>
         <v>0</v>
       </c>
       <c r="H41" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A41)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A41)</f>
         <v>0</v>
       </c>
       <c r="I41" s="8">
@@ -3301,7 +3141,7 @@
       <c r="N41" s="35"/>
     </row>
     <row r="42" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="67">
+      <c r="A42" s="58">
         <f t="shared" ref="A42:A104" si="9">IF(DAY(A41)=20,DATE(YEAR(A41),MONTH(A41)+1,5),DATE(YEAR(A41),MONTH(A41),20))</f>
         <v>506</v>
       </c>
@@ -3310,27 +3150,27 @@
         <v>34</v>
       </c>
       <c r="C42" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A42)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A42)</f>
         <v>0</v>
       </c>
       <c r="D42" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A42)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A42)</f>
         <v>0</v>
       </c>
       <c r="E42" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A42)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A42)</f>
         <v>0</v>
       </c>
       <c r="F42" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A42)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A42)</f>
         <v>0</v>
       </c>
       <c r="G42" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A42)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A42)</f>
         <v>0</v>
       </c>
       <c r="H42" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A42)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A42)</f>
         <v>0</v>
       </c>
       <c r="I42" s="8">
@@ -3352,7 +3192,7 @@
       <c r="N42" s="35"/>
     </row>
     <row r="43" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="67">
+      <c r="A43" s="58">
         <f t="shared" si="9"/>
         <v>522</v>
       </c>
@@ -3361,27 +3201,27 @@
         <v>35</v>
       </c>
       <c r="C43" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A43)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A43)</f>
         <v>0</v>
       </c>
       <c r="D43" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A43)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A43)</f>
         <v>0</v>
       </c>
       <c r="E43" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A43)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A43)</f>
         <v>0</v>
       </c>
       <c r="F43" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A43)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A43)</f>
         <v>0</v>
       </c>
       <c r="G43" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A43)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A43)</f>
         <v>0</v>
       </c>
       <c r="H43" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A43)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A43)</f>
         <v>0</v>
       </c>
       <c r="I43" s="8">
@@ -3403,7 +3243,7 @@
       <c r="N43" s="35"/>
     </row>
     <row r="44" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="67">
+      <c r="A44" s="58">
         <f t="shared" si="9"/>
         <v>537</v>
       </c>
@@ -3412,27 +3252,27 @@
         <v>36</v>
       </c>
       <c r="C44" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A44)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A44)</f>
         <v>0</v>
       </c>
       <c r="D44" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A44)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A44)</f>
         <v>0</v>
       </c>
       <c r="E44" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A44)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A44)</f>
         <v>0</v>
       </c>
       <c r="F44" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A44)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A44)</f>
         <v>0</v>
       </c>
       <c r="G44" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A44)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A44)</f>
         <v>0</v>
       </c>
       <c r="H44" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A44)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A44)</f>
         <v>0</v>
       </c>
       <c r="I44" s="8">
@@ -3454,7 +3294,7 @@
       <c r="N44" s="35"/>
     </row>
     <row r="45" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="67">
+      <c r="A45" s="58">
         <f t="shared" si="9"/>
         <v>552</v>
       </c>
@@ -3463,27 +3303,27 @@
         <v>37</v>
       </c>
       <c r="C45" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A45)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A45)</f>
         <v>0</v>
       </c>
       <c r="D45" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A45)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A45)</f>
         <v>0</v>
       </c>
       <c r="E45" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A45)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A45)</f>
         <v>0</v>
       </c>
       <c r="F45" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A45)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A45)</f>
         <v>0</v>
       </c>
       <c r="G45" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A45)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A45)</f>
         <v>0</v>
       </c>
       <c r="H45" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A45)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A45)</f>
         <v>0</v>
       </c>
       <c r="I45" s="8">
@@ -3505,7 +3345,7 @@
       <c r="N45" s="35"/>
     </row>
     <row r="46" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="67">
+      <c r="A46" s="58">
         <f t="shared" si="9"/>
         <v>567</v>
       </c>
@@ -3514,27 +3354,27 @@
         <v>38</v>
       </c>
       <c r="C46" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A46)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A46)</f>
         <v>0</v>
       </c>
       <c r="D46" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A46)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A46)</f>
         <v>0</v>
       </c>
       <c r="E46" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A46)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A46)</f>
         <v>0</v>
       </c>
       <c r="F46" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A46)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A46)</f>
         <v>0</v>
       </c>
       <c r="G46" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A46)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A46)</f>
         <v>0</v>
       </c>
       <c r="H46" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A46)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A46)</f>
         <v>0</v>
       </c>
       <c r="I46" s="8">
@@ -3556,7 +3396,7 @@
       <c r="N46" s="35"/>
     </row>
     <row r="47" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="67">
+      <c r="A47" s="58">
         <f t="shared" si="9"/>
         <v>583</v>
       </c>
@@ -3565,27 +3405,27 @@
         <v>39</v>
       </c>
       <c r="C47" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A47)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A47)</f>
         <v>0</v>
       </c>
       <c r="D47" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A47)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A47)</f>
         <v>0</v>
       </c>
       <c r="E47" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A47)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A47)</f>
         <v>0</v>
       </c>
       <c r="F47" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A47)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A47)</f>
         <v>0</v>
       </c>
       <c r="G47" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A47)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A47)</f>
         <v>0</v>
       </c>
       <c r="H47" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A47)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A47)</f>
         <v>0</v>
       </c>
       <c r="I47" s="8">
@@ -3607,7 +3447,7 @@
       <c r="N47" s="35"/>
     </row>
     <row r="48" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="67">
+      <c r="A48" s="58">
         <f t="shared" si="9"/>
         <v>598</v>
       </c>
@@ -3616,27 +3456,27 @@
         <v>40</v>
       </c>
       <c r="C48" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A48)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A48)</f>
         <v>0</v>
       </c>
       <c r="D48" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A48)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A48)</f>
         <v>0</v>
       </c>
       <c r="E48" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A48)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A48)</f>
         <v>0</v>
       </c>
       <c r="F48" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A48)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A48)</f>
         <v>0</v>
       </c>
       <c r="G48" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A48)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A48)</f>
         <v>0</v>
       </c>
       <c r="H48" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A48)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A48)</f>
         <v>0</v>
       </c>
       <c r="I48" s="8">
@@ -3658,7 +3498,7 @@
       <c r="N48" s="35"/>
     </row>
     <row r="49" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="67">
+      <c r="A49" s="58">
         <f t="shared" si="9"/>
         <v>614</v>
       </c>
@@ -3667,27 +3507,27 @@
         <v>41</v>
       </c>
       <c r="C49" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A49)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A49)</f>
         <v>0</v>
       </c>
       <c r="D49" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A49)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A49)</f>
         <v>0</v>
       </c>
       <c r="E49" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A49)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A49)</f>
         <v>0</v>
       </c>
       <c r="F49" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A49)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A49)</f>
         <v>0</v>
       </c>
       <c r="G49" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A49)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A49)</f>
         <v>0</v>
       </c>
       <c r="H49" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A49)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A49)</f>
         <v>0</v>
       </c>
       <c r="I49" s="8">
@@ -3709,7 +3549,7 @@
       <c r="N49" s="35"/>
     </row>
     <row r="50" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="67">
+      <c r="A50" s="58">
         <f t="shared" si="9"/>
         <v>629</v>
       </c>
@@ -3718,27 +3558,27 @@
         <v>42</v>
       </c>
       <c r="C50" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A50)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A50)</f>
         <v>0</v>
       </c>
       <c r="D50" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A50)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A50)</f>
         <v>0</v>
       </c>
       <c r="E50" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A50)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A50)</f>
         <v>0</v>
       </c>
       <c r="F50" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A50)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A50)</f>
         <v>0</v>
       </c>
       <c r="G50" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A50)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A50)</f>
         <v>0</v>
       </c>
       <c r="H50" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A50)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A50)</f>
         <v>0</v>
       </c>
       <c r="I50" s="8">
@@ -3760,7 +3600,7 @@
       <c r="N50" s="35"/>
     </row>
     <row r="51" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="67">
+      <c r="A51" s="58">
         <f t="shared" si="9"/>
         <v>644</v>
       </c>
@@ -3769,27 +3609,27 @@
         <v>43</v>
       </c>
       <c r="C51" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A51)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A51)</f>
         <v>0</v>
       </c>
       <c r="D51" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A51)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A51)</f>
         <v>0</v>
       </c>
       <c r="E51" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A51)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A51)</f>
         <v>0</v>
       </c>
       <c r="F51" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A51)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A51)</f>
         <v>0</v>
       </c>
       <c r="G51" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A51)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A51)</f>
         <v>0</v>
       </c>
       <c r="H51" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A51)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A51)</f>
         <v>0</v>
       </c>
       <c r="I51" s="8">
@@ -3811,7 +3651,7 @@
       <c r="N51" s="35"/>
     </row>
     <row r="52" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="67">
+      <c r="A52" s="58">
         <f t="shared" si="9"/>
         <v>659</v>
       </c>
@@ -3820,27 +3660,27 @@
         <v>44</v>
       </c>
       <c r="C52" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A52)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A52)</f>
         <v>0</v>
       </c>
       <c r="D52" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A52)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A52)</f>
         <v>0</v>
       </c>
       <c r="E52" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A52)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A52)</f>
         <v>0</v>
       </c>
       <c r="F52" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A52)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A52)</f>
         <v>0</v>
       </c>
       <c r="G52" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A52)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A52)</f>
         <v>0</v>
       </c>
       <c r="H52" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A52)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A52)</f>
         <v>0</v>
       </c>
       <c r="I52" s="8">
@@ -3862,7 +3702,7 @@
       <c r="N52" s="35"/>
     </row>
     <row r="53" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="67">
+      <c r="A53" s="58">
         <f t="shared" si="9"/>
         <v>675</v>
       </c>
@@ -3871,27 +3711,27 @@
         <v>45</v>
       </c>
       <c r="C53" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A53)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A53)</f>
         <v>0</v>
       </c>
       <c r="D53" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A53)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A53)</f>
         <v>0</v>
       </c>
       <c r="E53" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A53)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A53)</f>
         <v>0</v>
       </c>
       <c r="F53" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A53)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A53)</f>
         <v>0</v>
       </c>
       <c r="G53" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A53)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A53)</f>
         <v>0</v>
       </c>
       <c r="H53" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A53)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A53)</f>
         <v>0</v>
       </c>
       <c r="I53" s="8">
@@ -3913,7 +3753,7 @@
       <c r="N53" s="35"/>
     </row>
     <row r="54" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="67">
+      <c r="A54" s="58">
         <f t="shared" si="9"/>
         <v>690</v>
       </c>
@@ -3922,27 +3762,27 @@
         <v>46</v>
       </c>
       <c r="C54" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A54)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A54)</f>
         <v>0</v>
       </c>
       <c r="D54" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A54)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A54)</f>
         <v>0</v>
       </c>
       <c r="E54" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A54)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A54)</f>
         <v>0</v>
       </c>
       <c r="F54" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A54)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A54)</f>
         <v>0</v>
       </c>
       <c r="G54" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A54)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A54)</f>
         <v>0</v>
       </c>
       <c r="H54" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A54)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A54)</f>
         <v>0</v>
       </c>
       <c r="I54" s="8">
@@ -3964,7 +3804,7 @@
       <c r="N54" s="35"/>
     </row>
     <row r="55" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="67">
+      <c r="A55" s="58">
         <f t="shared" si="9"/>
         <v>705</v>
       </c>
@@ -3973,27 +3813,27 @@
         <v>47</v>
       </c>
       <c r="C55" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A55)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A55)</f>
         <v>0</v>
       </c>
       <c r="D55" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A55)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A55)</f>
         <v>0</v>
       </c>
       <c r="E55" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A55)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A55)</f>
         <v>0</v>
       </c>
       <c r="F55" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A55)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A55)</f>
         <v>0</v>
       </c>
       <c r="G55" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A55)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A55)</f>
         <v>0</v>
       </c>
       <c r="H55" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A55)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A55)</f>
         <v>0</v>
       </c>
       <c r="I55" s="8">
@@ -4015,7 +3855,7 @@
       <c r="N55" s="35"/>
     </row>
     <row r="56" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="67">
+      <c r="A56" s="58">
         <f t="shared" si="9"/>
         <v>720</v>
       </c>
@@ -4024,27 +3864,27 @@
         <v>48</v>
       </c>
       <c r="C56" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A56)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A56)</f>
         <v>0</v>
       </c>
       <c r="D56" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A56)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A56)</f>
         <v>0</v>
       </c>
       <c r="E56" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A56)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A56)</f>
         <v>0</v>
       </c>
       <c r="F56" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A56)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A56)</f>
         <v>0</v>
       </c>
       <c r="G56" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A56)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A56)</f>
         <v>0</v>
       </c>
       <c r="H56" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A56)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A56)</f>
         <v>0</v>
       </c>
       <c r="I56" s="8">
@@ -4066,7 +3906,7 @@
       <c r="N56" s="35"/>
     </row>
     <row r="57" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="67">
+      <c r="A57" s="58">
         <f t="shared" si="9"/>
         <v>736</v>
       </c>
@@ -4075,27 +3915,27 @@
         <v>49</v>
       </c>
       <c r="C57" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A57)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A57)</f>
         <v>0</v>
       </c>
       <c r="D57" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A57)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A57)</f>
         <v>0</v>
       </c>
       <c r="E57" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A57)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A57)</f>
         <v>0</v>
       </c>
       <c r="F57" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A57)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A57)</f>
         <v>0</v>
       </c>
       <c r="G57" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A57)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A57)</f>
         <v>0</v>
       </c>
       <c r="H57" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A57)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A57)</f>
         <v>0</v>
       </c>
       <c r="I57" s="8">
@@ -4117,7 +3957,7 @@
       <c r="N57" s="35"/>
     </row>
     <row r="58" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="67">
+      <c r="A58" s="58">
         <f t="shared" si="9"/>
         <v>751</v>
       </c>
@@ -4126,27 +3966,27 @@
         <v>50</v>
       </c>
       <c r="C58" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A58)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A58)</f>
         <v>0</v>
       </c>
       <c r="D58" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A58)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A58)</f>
         <v>0</v>
       </c>
       <c r="E58" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A58)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A58)</f>
         <v>0</v>
       </c>
       <c r="F58" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A58)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A58)</f>
         <v>0</v>
       </c>
       <c r="G58" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A58)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A58)</f>
         <v>0</v>
       </c>
       <c r="H58" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A58)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A58)</f>
         <v>0</v>
       </c>
       <c r="I58" s="8">
@@ -4168,7 +4008,7 @@
       <c r="N58" s="35"/>
     </row>
     <row r="59" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="67">
+      <c r="A59" s="58">
         <f t="shared" si="9"/>
         <v>767</v>
       </c>
@@ -4177,27 +4017,27 @@
         <v>51</v>
       </c>
       <c r="C59" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A59)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A59)</f>
         <v>0</v>
       </c>
       <c r="D59" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A59)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A59)</f>
         <v>0</v>
       </c>
       <c r="E59" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A59)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A59)</f>
         <v>0</v>
       </c>
       <c r="F59" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A59)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A59)</f>
         <v>0</v>
       </c>
       <c r="G59" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A59)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A59)</f>
         <v>0</v>
       </c>
       <c r="H59" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A59)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A59)</f>
         <v>0</v>
       </c>
       <c r="I59" s="8">
@@ -4219,7 +4059,7 @@
       <c r="N59" s="35"/>
     </row>
     <row r="60" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="67">
+      <c r="A60" s="58">
         <f t="shared" si="9"/>
         <v>782</v>
       </c>
@@ -4228,27 +4068,27 @@
         <v>52</v>
       </c>
       <c r="C60" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A60)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A60)</f>
         <v>0</v>
       </c>
       <c r="D60" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A60)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A60)</f>
         <v>0</v>
       </c>
       <c r="E60" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A60)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A60)</f>
         <v>0</v>
       </c>
       <c r="F60" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A60)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A60)</f>
         <v>0</v>
       </c>
       <c r="G60" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A60)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A60)</f>
         <v>0</v>
       </c>
       <c r="H60" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A60)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A60)</f>
         <v>0</v>
       </c>
       <c r="I60" s="8">
@@ -4270,7 +4110,7 @@
       <c r="N60" s="35"/>
     </row>
     <row r="61" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="67">
+      <c r="A61" s="58">
         <f t="shared" si="9"/>
         <v>795</v>
       </c>
@@ -4279,27 +4119,27 @@
         <v>53</v>
       </c>
       <c r="C61" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A61)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A61)</f>
         <v>0</v>
       </c>
       <c r="D61" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A61)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A61)</f>
         <v>0</v>
       </c>
       <c r="E61" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A61)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A61)</f>
         <v>0</v>
       </c>
       <c r="F61" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A61)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A61)</f>
         <v>0</v>
       </c>
       <c r="G61" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A61)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A61)</f>
         <v>0</v>
       </c>
       <c r="H61" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A61)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A61)</f>
         <v>0</v>
       </c>
       <c r="I61" s="8">
@@ -4321,7 +4161,7 @@
       <c r="N61" s="35"/>
     </row>
     <row r="62" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="67">
+      <c r="A62" s="58">
         <f t="shared" si="9"/>
         <v>810</v>
       </c>
@@ -4330,27 +4170,27 @@
         <v>54</v>
       </c>
       <c r="C62" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A62)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A62)</f>
         <v>0</v>
       </c>
       <c r="D62" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A62)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A62)</f>
         <v>0</v>
       </c>
       <c r="E62" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A62)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A62)</f>
         <v>0</v>
       </c>
       <c r="F62" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A62)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A62)</f>
         <v>0</v>
       </c>
       <c r="G62" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A62)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A62)</f>
         <v>0</v>
       </c>
       <c r="H62" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A62)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A62)</f>
         <v>0</v>
       </c>
       <c r="I62" s="8">
@@ -4372,7 +4212,7 @@
       <c r="N62" s="35"/>
     </row>
     <row r="63" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="67">
+      <c r="A63" s="58">
         <f t="shared" si="9"/>
         <v>826</v>
       </c>
@@ -4381,27 +4221,27 @@
         <v>55</v>
       </c>
       <c r="C63" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A63)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A63)</f>
         <v>0</v>
       </c>
       <c r="D63" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A63)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A63)</f>
         <v>0</v>
       </c>
       <c r="E63" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A63)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A63)</f>
         <v>0</v>
       </c>
       <c r="F63" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A63)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A63)</f>
         <v>0</v>
       </c>
       <c r="G63" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A63)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A63)</f>
         <v>0</v>
       </c>
       <c r="H63" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A63)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A63)</f>
         <v>0</v>
       </c>
       <c r="I63" s="8">
@@ -4423,7 +4263,7 @@
       <c r="N63" s="35"/>
     </row>
     <row r="64" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="67">
+      <c r="A64" s="58">
         <f t="shared" si="9"/>
         <v>841</v>
       </c>
@@ -4432,27 +4272,27 @@
         <v>56</v>
       </c>
       <c r="C64" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A64)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A64)</f>
         <v>0</v>
       </c>
       <c r="D64" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A64)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A64)</f>
         <v>0</v>
       </c>
       <c r="E64" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A64)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A64)</f>
         <v>0</v>
       </c>
       <c r="F64" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A64)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A64)</f>
         <v>0</v>
       </c>
       <c r="G64" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A64)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A64)</f>
         <v>0</v>
       </c>
       <c r="H64" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A64)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A64)</f>
         <v>0</v>
       </c>
       <c r="I64" s="8">
@@ -4474,7 +4314,7 @@
       <c r="N64" s="35"/>
     </row>
     <row r="65" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="67">
+      <c r="A65" s="58">
         <f t="shared" si="9"/>
         <v>856</v>
       </c>
@@ -4483,27 +4323,27 @@
         <v>57</v>
       </c>
       <c r="C65" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A65)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A65)</f>
         <v>0</v>
       </c>
       <c r="D65" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A65)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A65)</f>
         <v>0</v>
       </c>
       <c r="E65" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A65)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A65)</f>
         <v>0</v>
       </c>
       <c r="F65" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A65)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A65)</f>
         <v>0</v>
       </c>
       <c r="G65" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A65)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A65)</f>
         <v>0</v>
       </c>
       <c r="H65" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A65)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A65)</f>
         <v>0</v>
       </c>
       <c r="I65" s="8">
@@ -4525,7 +4365,7 @@
       <c r="N65" s="35"/>
     </row>
     <row r="66" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="67">
+      <c r="A66" s="58">
         <f t="shared" si="9"/>
         <v>871</v>
       </c>
@@ -4534,27 +4374,27 @@
         <v>58</v>
       </c>
       <c r="C66" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A66)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A66)</f>
         <v>0</v>
       </c>
       <c r="D66" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A66)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A66)</f>
         <v>0</v>
       </c>
       <c r="E66" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A66)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A66)</f>
         <v>0</v>
       </c>
       <c r="F66" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A66)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A66)</f>
         <v>0</v>
       </c>
       <c r="G66" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A66)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A66)</f>
         <v>0</v>
       </c>
       <c r="H66" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A66)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A66)</f>
         <v>0</v>
       </c>
       <c r="I66" s="8">
@@ -4576,7 +4416,7 @@
       <c r="N66" s="35"/>
     </row>
     <row r="67" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="67">
+      <c r="A67" s="58">
         <f t="shared" si="9"/>
         <v>887</v>
       </c>
@@ -4585,27 +4425,27 @@
         <v>59</v>
       </c>
       <c r="C67" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A67)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A67)</f>
         <v>0</v>
       </c>
       <c r="D67" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A67)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A67)</f>
         <v>0</v>
       </c>
       <c r="E67" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A67)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A67)</f>
         <v>0</v>
       </c>
       <c r="F67" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A67)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A67)</f>
         <v>0</v>
       </c>
       <c r="G67" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A67)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A67)</f>
         <v>0</v>
       </c>
       <c r="H67" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A67)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A67)</f>
         <v>0</v>
       </c>
       <c r="I67" s="8">
@@ -4627,7 +4467,7 @@
       <c r="N67" s="35"/>
     </row>
     <row r="68" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="67">
+      <c r="A68" s="58">
         <f t="shared" si="9"/>
         <v>902</v>
       </c>
@@ -4636,27 +4476,27 @@
         <v>60</v>
       </c>
       <c r="C68" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A68)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A68)</f>
         <v>0</v>
       </c>
       <c r="D68" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A68)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A68)</f>
         <v>0</v>
       </c>
       <c r="E68" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A68)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A68)</f>
         <v>0</v>
       </c>
       <c r="F68" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A68)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A68)</f>
         <v>0</v>
       </c>
       <c r="G68" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A68)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A68)</f>
         <v>0</v>
       </c>
       <c r="H68" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A68)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A68)</f>
         <v>0</v>
       </c>
       <c r="I68" s="8">
@@ -4678,7 +4518,7 @@
       <c r="N68" s="35"/>
     </row>
     <row r="69" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="67">
+      <c r="A69" s="58">
         <f t="shared" si="9"/>
         <v>917</v>
       </c>
@@ -4687,27 +4527,27 @@
         <v>61</v>
       </c>
       <c r="C69" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A69)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A69)</f>
         <v>0</v>
       </c>
       <c r="D69" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A69)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A69)</f>
         <v>0</v>
       </c>
       <c r="E69" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A69)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A69)</f>
         <v>0</v>
       </c>
       <c r="F69" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A69)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A69)</f>
         <v>0</v>
       </c>
       <c r="G69" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A69)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A69)</f>
         <v>0</v>
       </c>
       <c r="H69" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A69)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A69)</f>
         <v>0</v>
       </c>
       <c r="I69" s="8">
@@ -4729,7 +4569,7 @@
       <c r="N69" s="35"/>
     </row>
     <row r="70" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="67">
+      <c r="A70" s="58">
         <f t="shared" si="9"/>
         <v>932</v>
       </c>
@@ -4738,27 +4578,27 @@
         <v>62</v>
       </c>
       <c r="C70" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A70)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A70)</f>
         <v>0</v>
       </c>
       <c r="D70" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A70)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A70)</f>
         <v>0</v>
       </c>
       <c r="E70" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A70)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A70)</f>
         <v>0</v>
       </c>
       <c r="F70" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A70)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A70)</f>
         <v>0</v>
       </c>
       <c r="G70" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A70)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A70)</f>
         <v>0</v>
       </c>
       <c r="H70" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A70)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A70)</f>
         <v>0</v>
       </c>
       <c r="I70" s="8">
@@ -4780,7 +4620,7 @@
       <c r="N70" s="35"/>
     </row>
     <row r="71" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="67">
+      <c r="A71" s="58">
         <f t="shared" si="9"/>
         <v>948</v>
       </c>
@@ -4789,27 +4629,27 @@
         <v>63</v>
       </c>
       <c r="C71" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A71)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A71)</f>
         <v>0</v>
       </c>
       <c r="D71" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A71)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A71)</f>
         <v>0</v>
       </c>
       <c r="E71" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A71)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A71)</f>
         <v>0</v>
       </c>
       <c r="F71" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A71)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A71)</f>
         <v>0</v>
       </c>
       <c r="G71" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A71)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A71)</f>
         <v>0</v>
       </c>
       <c r="H71" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A71)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A71)</f>
         <v>0</v>
       </c>
       <c r="I71" s="8">
@@ -4831,7 +4671,7 @@
       <c r="N71" s="35"/>
     </row>
     <row r="72" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="67">
+      <c r="A72" s="58">
         <f t="shared" si="9"/>
         <v>963</v>
       </c>
@@ -4840,27 +4680,27 @@
         <v>64</v>
       </c>
       <c r="C72" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A72)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A72)</f>
         <v>0</v>
       </c>
       <c r="D72" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A72)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A72)</f>
         <v>0</v>
       </c>
       <c r="E72" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A72)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A72)</f>
         <v>0</v>
       </c>
       <c r="F72" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A72)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A72)</f>
         <v>0</v>
       </c>
       <c r="G72" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A72)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A72)</f>
         <v>0</v>
       </c>
       <c r="H72" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A72)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A72)</f>
         <v>0</v>
       </c>
       <c r="I72" s="8">
@@ -4882,7 +4722,7 @@
       <c r="N72" s="35"/>
     </row>
     <row r="73" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="67">
+      <c r="A73" s="58">
         <f t="shared" si="9"/>
         <v>979</v>
       </c>
@@ -4891,27 +4731,27 @@
         <v>65</v>
       </c>
       <c r="C73" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A73)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A73)</f>
         <v>0</v>
       </c>
       <c r="D73" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A73)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A73)</f>
         <v>0</v>
       </c>
       <c r="E73" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A73)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A73)</f>
         <v>0</v>
       </c>
       <c r="F73" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A73)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A73)</f>
         <v>0</v>
       </c>
       <c r="G73" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A73)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A73)</f>
         <v>0</v>
       </c>
       <c r="H73" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A73)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A73)</f>
         <v>0</v>
       </c>
       <c r="I73" s="8">
@@ -4933,7 +4773,7 @@
       <c r="N73" s="35"/>
     </row>
     <row r="74" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="67">
+      <c r="A74" s="58">
         <f t="shared" si="9"/>
         <v>994</v>
       </c>
@@ -4942,27 +4782,27 @@
         <v>66</v>
       </c>
       <c r="C74" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A74)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A74)</f>
         <v>0</v>
       </c>
       <c r="D74" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A74)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A74)</f>
         <v>0</v>
       </c>
       <c r="E74" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A74)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A74)</f>
         <v>0</v>
       </c>
       <c r="F74" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A74)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A74)</f>
         <v>0</v>
       </c>
       <c r="G74" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A74)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A74)</f>
         <v>0</v>
       </c>
       <c r="H74" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A74)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A74)</f>
         <v>0</v>
       </c>
       <c r="I74" s="8">
@@ -4984,7 +4824,7 @@
       <c r="N74" s="35"/>
     </row>
     <row r="75" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="67">
+      <c r="A75" s="58">
         <f t="shared" si="9"/>
         <v>1009</v>
       </c>
@@ -4993,27 +4833,27 @@
         <v>67</v>
       </c>
       <c r="C75" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A75)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A75)</f>
         <v>0</v>
       </c>
       <c r="D75" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A75)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A75)</f>
         <v>0</v>
       </c>
       <c r="E75" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A75)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A75)</f>
         <v>0</v>
       </c>
       <c r="F75" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A75)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A75)</f>
         <v>0</v>
       </c>
       <c r="G75" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A75)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A75)</f>
         <v>0</v>
       </c>
       <c r="H75" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A75)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A75)</f>
         <v>0</v>
       </c>
       <c r="I75" s="8">
@@ -5035,7 +4875,7 @@
       <c r="N75" s="35"/>
     </row>
     <row r="76" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="67">
+      <c r="A76" s="58">
         <f t="shared" si="9"/>
         <v>1024</v>
       </c>
@@ -5044,27 +4884,27 @@
         <v>68</v>
       </c>
       <c r="C76" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A76)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A76)</f>
         <v>0</v>
       </c>
       <c r="D76" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A76)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A76)</f>
         <v>0</v>
       </c>
       <c r="E76" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A76)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A76)</f>
         <v>0</v>
       </c>
       <c r="F76" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A76)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A76)</f>
         <v>0</v>
       </c>
       <c r="G76" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A76)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A76)</f>
         <v>0</v>
       </c>
       <c r="H76" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A76)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A76)</f>
         <v>0</v>
       </c>
       <c r="I76" s="8">
@@ -5086,7 +4926,7 @@
       <c r="N76" s="35"/>
     </row>
     <row r="77" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="67">
+      <c r="A77" s="58">
         <f t="shared" si="9"/>
         <v>1040</v>
       </c>
@@ -5095,27 +4935,27 @@
         <v>69</v>
       </c>
       <c r="C77" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A77)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A77)</f>
         <v>0</v>
       </c>
       <c r="D77" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A77)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A77)</f>
         <v>0</v>
       </c>
       <c r="E77" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A77)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A77)</f>
         <v>0</v>
       </c>
       <c r="F77" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A77)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A77)</f>
         <v>0</v>
       </c>
       <c r="G77" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A77)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A77)</f>
         <v>0</v>
       </c>
       <c r="H77" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A77)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A77)</f>
         <v>0</v>
       </c>
       <c r="I77" s="8">
@@ -5137,7 +4977,7 @@
       <c r="N77" s="35"/>
     </row>
     <row r="78" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="67">
+      <c r="A78" s="58">
         <f t="shared" si="9"/>
         <v>1055</v>
       </c>
@@ -5146,27 +4986,27 @@
         <v>70</v>
       </c>
       <c r="C78" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A78)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A78)</f>
         <v>0</v>
       </c>
       <c r="D78" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A78)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A78)</f>
         <v>0</v>
       </c>
       <c r="E78" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A78)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A78)</f>
         <v>0</v>
       </c>
       <c r="F78" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A78)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A78)</f>
         <v>0</v>
       </c>
       <c r="G78" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A78)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A78)</f>
         <v>0</v>
       </c>
       <c r="H78" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A78)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A78)</f>
         <v>0</v>
       </c>
       <c r="I78" s="8">
@@ -5188,7 +5028,7 @@
       <c r="N78" s="35"/>
     </row>
     <row r="79" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="67">
+      <c r="A79" s="58">
         <f t="shared" si="9"/>
         <v>1070</v>
       </c>
@@ -5197,27 +5037,27 @@
         <v>71</v>
       </c>
       <c r="C79" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A79)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A79)</f>
         <v>0</v>
       </c>
       <c r="D79" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A79)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A79)</f>
         <v>0</v>
       </c>
       <c r="E79" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A79)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A79)</f>
         <v>0</v>
       </c>
       <c r="F79" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A79)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A79)</f>
         <v>0</v>
       </c>
       <c r="G79" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A79)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A79)</f>
         <v>0</v>
       </c>
       <c r="H79" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A79)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A79)</f>
         <v>0</v>
       </c>
       <c r="I79" s="8">
@@ -5239,7 +5079,7 @@
       <c r="N79" s="35"/>
     </row>
     <row r="80" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="67">
+      <c r="A80" s="58">
         <f t="shared" si="9"/>
         <v>1085</v>
       </c>
@@ -5248,27 +5088,27 @@
         <v>72</v>
       </c>
       <c r="C80" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A80)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A80)</f>
         <v>0</v>
       </c>
       <c r="D80" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A80)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A80)</f>
         <v>0</v>
       </c>
       <c r="E80" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A80)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A80)</f>
         <v>0</v>
       </c>
       <c r="F80" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A80)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A80)</f>
         <v>0</v>
       </c>
       <c r="G80" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A80)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A80)</f>
         <v>0</v>
       </c>
       <c r="H80" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A80)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A80)</f>
         <v>0</v>
       </c>
       <c r="I80" s="8">
@@ -5290,7 +5130,7 @@
       <c r="N80" s="35"/>
     </row>
     <row r="81" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="67">
+      <c r="A81" s="58">
         <f t="shared" si="9"/>
         <v>1101</v>
       </c>
@@ -5299,27 +5139,27 @@
         <v>73</v>
       </c>
       <c r="C81" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A81)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A81)</f>
         <v>0</v>
       </c>
       <c r="D81" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A81)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A81)</f>
         <v>0</v>
       </c>
       <c r="E81" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A81)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A81)</f>
         <v>0</v>
       </c>
       <c r="F81" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A81)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A81)</f>
         <v>0</v>
       </c>
       <c r="G81" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A81)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A81)</f>
         <v>0</v>
       </c>
       <c r="H81" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A81)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A81)</f>
         <v>0</v>
       </c>
       <c r="I81" s="8">
@@ -5341,7 +5181,7 @@
       <c r="N81" s="35"/>
     </row>
     <row r="82" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="67">
+      <c r="A82" s="58">
         <f t="shared" si="9"/>
         <v>1116</v>
       </c>
@@ -5350,27 +5190,27 @@
         <v>74</v>
       </c>
       <c r="C82" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A82)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A82)</f>
         <v>0</v>
       </c>
       <c r="D82" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A82)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A82)</f>
         <v>0</v>
       </c>
       <c r="E82" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A82)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A82)</f>
         <v>0</v>
       </c>
       <c r="F82" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A82)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A82)</f>
         <v>0</v>
       </c>
       <c r="G82" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A82)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A82)</f>
         <v>0</v>
       </c>
       <c r="H82" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A82)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A82)</f>
         <v>0</v>
       </c>
       <c r="I82" s="8">
@@ -5392,7 +5232,7 @@
       <c r="N82" s="35"/>
     </row>
     <row r="83" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="67">
+      <c r="A83" s="58">
         <f t="shared" si="9"/>
         <v>1132</v>
       </c>
@@ -5401,27 +5241,27 @@
         <v>75</v>
       </c>
       <c r="C83" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A83)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A83)</f>
         <v>0</v>
       </c>
       <c r="D83" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A83)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A83)</f>
         <v>0</v>
       </c>
       <c r="E83" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A83)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A83)</f>
         <v>0</v>
       </c>
       <c r="F83" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A83)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A83)</f>
         <v>0</v>
       </c>
       <c r="G83" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A83)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A83)</f>
         <v>0</v>
       </c>
       <c r="H83" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A83)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A83)</f>
         <v>0</v>
       </c>
       <c r="I83" s="8">
@@ -5443,7 +5283,7 @@
       <c r="N83" s="35"/>
     </row>
     <row r="84" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="67">
+      <c r="A84" s="58">
         <f t="shared" si="9"/>
         <v>1147</v>
       </c>
@@ -5452,27 +5292,27 @@
         <v>76</v>
       </c>
       <c r="C84" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A84)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A84)</f>
         <v>0</v>
       </c>
       <c r="D84" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A84)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A84)</f>
         <v>0</v>
       </c>
       <c r="E84" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A84)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A84)</f>
         <v>0</v>
       </c>
       <c r="F84" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A84)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A84)</f>
         <v>0</v>
       </c>
       <c r="G84" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A84)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A84)</f>
         <v>0</v>
       </c>
       <c r="H84" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A84)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A84)</f>
         <v>0</v>
       </c>
       <c r="I84" s="8">
@@ -5494,7 +5334,7 @@
       <c r="N84" s="35"/>
     </row>
     <row r="85" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="67">
+      <c r="A85" s="58">
         <f t="shared" si="9"/>
         <v>1160</v>
       </c>
@@ -5503,27 +5343,27 @@
         <v>77</v>
       </c>
       <c r="C85" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A85)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A85)</f>
         <v>0</v>
       </c>
       <c r="D85" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A85)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A85)</f>
         <v>0</v>
       </c>
       <c r="E85" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A85)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A85)</f>
         <v>0</v>
       </c>
       <c r="F85" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A85)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A85)</f>
         <v>0</v>
       </c>
       <c r="G85" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A85)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A85)</f>
         <v>0</v>
       </c>
       <c r="H85" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A85)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A85)</f>
         <v>0</v>
       </c>
       <c r="I85" s="8">
@@ -5545,7 +5385,7 @@
       <c r="N85" s="35"/>
     </row>
     <row r="86" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="67">
+      <c r="A86" s="58">
         <f t="shared" si="9"/>
         <v>1175</v>
       </c>
@@ -5554,27 +5394,27 @@
         <v>78</v>
       </c>
       <c r="C86" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A86)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A86)</f>
         <v>0</v>
       </c>
       <c r="D86" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A86)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A86)</f>
         <v>0</v>
       </c>
       <c r="E86" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A86)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A86)</f>
         <v>0</v>
       </c>
       <c r="F86" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A86)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A86)</f>
         <v>0</v>
       </c>
       <c r="G86" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A86)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A86)</f>
         <v>0</v>
       </c>
       <c r="H86" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A86)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A86)</f>
         <v>0</v>
       </c>
       <c r="I86" s="8">
@@ -5596,7 +5436,7 @@
       <c r="N86" s="35"/>
     </row>
     <row r="87" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="67">
+      <c r="A87" s="58">
         <f t="shared" si="9"/>
         <v>1191</v>
       </c>
@@ -5605,27 +5445,27 @@
         <v>79</v>
       </c>
       <c r="C87" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A87)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A87)</f>
         <v>0</v>
       </c>
       <c r="D87" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A87)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A87)</f>
         <v>0</v>
       </c>
       <c r="E87" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A87)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A87)</f>
         <v>0</v>
       </c>
       <c r="F87" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A87)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A87)</f>
         <v>0</v>
       </c>
       <c r="G87" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A87)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A87)</f>
         <v>0</v>
       </c>
       <c r="H87" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A87)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A87)</f>
         <v>0</v>
       </c>
       <c r="I87" s="8">
@@ -5647,7 +5487,7 @@
       <c r="N87" s="35"/>
     </row>
     <row r="88" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="67">
+      <c r="A88" s="58">
         <f t="shared" si="9"/>
         <v>1206</v>
       </c>
@@ -5656,27 +5496,27 @@
         <v>80</v>
       </c>
       <c r="C88" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A88)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A88)</f>
         <v>0</v>
       </c>
       <c r="D88" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A88)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A88)</f>
         <v>0</v>
       </c>
       <c r="E88" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A88)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A88)</f>
         <v>0</v>
       </c>
       <c r="F88" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A88)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A88)</f>
         <v>0</v>
       </c>
       <c r="G88" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A88)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A88)</f>
         <v>0</v>
       </c>
       <c r="H88" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A88)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A88)</f>
         <v>0</v>
       </c>
       <c r="I88" s="8">
@@ -5698,7 +5538,7 @@
       <c r="N88" s="35"/>
     </row>
     <row r="89" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="67">
+      <c r="A89" s="58">
         <f t="shared" si="9"/>
         <v>1221</v>
       </c>
@@ -5707,27 +5547,27 @@
         <v>81</v>
       </c>
       <c r="C89" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A89)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A89)</f>
         <v>0</v>
       </c>
       <c r="D89" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A89)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A89)</f>
         <v>0</v>
       </c>
       <c r="E89" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A89)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A89)</f>
         <v>0</v>
       </c>
       <c r="F89" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A89)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A89)</f>
         <v>0</v>
       </c>
       <c r="G89" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A89)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A89)</f>
         <v>0</v>
       </c>
       <c r="H89" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A89)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A89)</f>
         <v>0</v>
       </c>
       <c r="I89" s="8">
@@ -5749,7 +5589,7 @@
       <c r="N89" s="35"/>
     </row>
     <row r="90" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="67">
+      <c r="A90" s="58">
         <f t="shared" si="9"/>
         <v>1236</v>
       </c>
@@ -5758,27 +5598,27 @@
         <v>82</v>
       </c>
       <c r="C90" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A90)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A90)</f>
         <v>0</v>
       </c>
       <c r="D90" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A90)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A90)</f>
         <v>0</v>
       </c>
       <c r="E90" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A90)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A90)</f>
         <v>0</v>
       </c>
       <c r="F90" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A90)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A90)</f>
         <v>0</v>
       </c>
       <c r="G90" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A90)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A90)</f>
         <v>0</v>
       </c>
       <c r="H90" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A90)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A90)</f>
         <v>0</v>
       </c>
       <c r="I90" s="8">
@@ -5800,7 +5640,7 @@
       <c r="N90" s="35"/>
     </row>
     <row r="91" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="67">
+      <c r="A91" s="58">
         <f t="shared" si="9"/>
         <v>1252</v>
       </c>
@@ -5809,27 +5649,27 @@
         <v>83</v>
       </c>
       <c r="C91" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A91)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A91)</f>
         <v>0</v>
       </c>
       <c r="D91" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A91)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A91)</f>
         <v>0</v>
       </c>
       <c r="E91" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A91)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A91)</f>
         <v>0</v>
       </c>
       <c r="F91" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A91)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A91)</f>
         <v>0</v>
       </c>
       <c r="G91" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A91)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A91)</f>
         <v>0</v>
       </c>
       <c r="H91" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A91)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A91)</f>
         <v>0</v>
       </c>
       <c r="I91" s="8">
@@ -5851,7 +5691,7 @@
       <c r="N91" s="35"/>
     </row>
     <row r="92" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="67">
+      <c r="A92" s="58">
         <f t="shared" si="9"/>
         <v>1267</v>
       </c>
@@ -5860,27 +5700,27 @@
         <v>84</v>
       </c>
       <c r="C92" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A92)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A92)</f>
         <v>0</v>
       </c>
       <c r="D92" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A92)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A92)</f>
         <v>0</v>
       </c>
       <c r="E92" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A92)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A92)</f>
         <v>0</v>
       </c>
       <c r="F92" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A92)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A92)</f>
         <v>0</v>
       </c>
       <c r="G92" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A92)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A92)</f>
         <v>0</v>
       </c>
       <c r="H92" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A92)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A92)</f>
         <v>0</v>
       </c>
       <c r="I92" s="8">
@@ -5902,7 +5742,7 @@
       <c r="N92" s="35"/>
     </row>
     <row r="93" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="67">
+      <c r="A93" s="58">
         <f t="shared" si="9"/>
         <v>1282</v>
       </c>
@@ -5911,27 +5751,27 @@
         <v>85</v>
       </c>
       <c r="C93" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A93)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A93)</f>
         <v>0</v>
       </c>
       <c r="D93" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A93)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A93)</f>
         <v>0</v>
       </c>
       <c r="E93" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A93)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A93)</f>
         <v>0</v>
       </c>
       <c r="F93" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A93)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A93)</f>
         <v>0</v>
       </c>
       <c r="G93" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A93)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A93)</f>
         <v>0</v>
       </c>
       <c r="H93" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A93)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A93)</f>
         <v>0</v>
       </c>
       <c r="I93" s="8">
@@ -5953,7 +5793,7 @@
       <c r="N93" s="35"/>
     </row>
     <row r="94" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="67">
+      <c r="A94" s="58">
         <f t="shared" si="9"/>
         <v>1297</v>
       </c>
@@ -5962,27 +5802,27 @@
         <v>86</v>
       </c>
       <c r="C94" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A94)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A94)</f>
         <v>0</v>
       </c>
       <c r="D94" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A94)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A94)</f>
         <v>0</v>
       </c>
       <c r="E94" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A94)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A94)</f>
         <v>0</v>
       </c>
       <c r="F94" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A94)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A94)</f>
         <v>0</v>
       </c>
       <c r="G94" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A94)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A94)</f>
         <v>0</v>
       </c>
       <c r="H94" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A94)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A94)</f>
         <v>0</v>
       </c>
       <c r="I94" s="8">
@@ -6004,7 +5844,7 @@
       <c r="N94" s="35"/>
     </row>
     <row r="95" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="67">
+      <c r="A95" s="58">
         <f t="shared" si="9"/>
         <v>1313</v>
       </c>
@@ -6013,27 +5853,27 @@
         <v>87</v>
       </c>
       <c r="C95" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A95)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A95)</f>
         <v>0</v>
       </c>
       <c r="D95" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A95)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A95)</f>
         <v>0</v>
       </c>
       <c r="E95" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A95)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A95)</f>
         <v>0</v>
       </c>
       <c r="F95" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A95)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A95)</f>
         <v>0</v>
       </c>
       <c r="G95" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A95)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A95)</f>
         <v>0</v>
       </c>
       <c r="H95" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A95)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A95)</f>
         <v>0</v>
       </c>
       <c r="I95" s="8">
@@ -6055,7 +5895,7 @@
       <c r="N95" s="35"/>
     </row>
     <row r="96" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="67">
+      <c r="A96" s="58">
         <f t="shared" si="9"/>
         <v>1328</v>
       </c>
@@ -6064,27 +5904,27 @@
         <v>88</v>
       </c>
       <c r="C96" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A96)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A96)</f>
         <v>0</v>
       </c>
       <c r="D96" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A96)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A96)</f>
         <v>0</v>
       </c>
       <c r="E96" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A96)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A96)</f>
         <v>0</v>
       </c>
       <c r="F96" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A96)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A96)</f>
         <v>0</v>
       </c>
       <c r="G96" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A96)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A96)</f>
         <v>0</v>
       </c>
       <c r="H96" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A96)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A96)</f>
         <v>0</v>
       </c>
       <c r="I96" s="8">
@@ -6106,7 +5946,7 @@
       <c r="N96" s="35"/>
     </row>
     <row r="97" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="67">
+      <c r="A97" s="58">
         <f t="shared" si="9"/>
         <v>1344</v>
       </c>
@@ -6115,27 +5955,27 @@
         <v>89</v>
       </c>
       <c r="C97" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A97)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A97)</f>
         <v>0</v>
       </c>
       <c r="D97" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A97)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A97)</f>
         <v>0</v>
       </c>
       <c r="E97" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A97)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A97)</f>
         <v>0</v>
       </c>
       <c r="F97" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A97)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A97)</f>
         <v>0</v>
       </c>
       <c r="G97" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A97)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A97)</f>
         <v>0</v>
       </c>
       <c r="H97" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A97)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A97)</f>
         <v>0</v>
       </c>
       <c r="I97" s="8">
@@ -6157,7 +5997,7 @@
       <c r="N97" s="35"/>
     </row>
     <row r="98" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="67">
+      <c r="A98" s="58">
         <f t="shared" si="9"/>
         <v>1359</v>
       </c>
@@ -6166,27 +6006,27 @@
         <v>90</v>
       </c>
       <c r="C98" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A98)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A98)</f>
         <v>0</v>
       </c>
       <c r="D98" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A98)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A98)</f>
         <v>0</v>
       </c>
       <c r="E98" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A98)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A98)</f>
         <v>0</v>
       </c>
       <c r="F98" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A98)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A98)</f>
         <v>0</v>
       </c>
       <c r="G98" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A98)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A98)</f>
         <v>0</v>
       </c>
       <c r="H98" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A98)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A98)</f>
         <v>0</v>
       </c>
       <c r="I98" s="8">
@@ -6208,7 +6048,7 @@
       <c r="N98" s="35"/>
     </row>
     <row r="99" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="67">
+      <c r="A99" s="58">
         <f t="shared" si="9"/>
         <v>1374</v>
       </c>
@@ -6217,27 +6057,27 @@
         <v>91</v>
       </c>
       <c r="C99" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A99)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A99)</f>
         <v>0</v>
       </c>
       <c r="D99" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A99)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A99)</f>
         <v>0</v>
       </c>
       <c r="E99" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A99)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A99)</f>
         <v>0</v>
       </c>
       <c r="F99" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A99)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A99)</f>
         <v>0</v>
       </c>
       <c r="G99" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A99)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A99)</f>
         <v>0</v>
       </c>
       <c r="H99" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A99)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A99)</f>
         <v>0</v>
       </c>
       <c r="I99" s="8">
@@ -6259,7 +6099,7 @@
       <c r="N99" s="35"/>
     </row>
     <row r="100" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="67">
+      <c r="A100" s="58">
         <f t="shared" si="9"/>
         <v>1389</v>
       </c>
@@ -6268,27 +6108,27 @@
         <v>92</v>
       </c>
       <c r="C100" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A100)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A100)</f>
         <v>0</v>
       </c>
       <c r="D100" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A100)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A100)</f>
         <v>0</v>
       </c>
       <c r="E100" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A100)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A100)</f>
         <v>0</v>
       </c>
       <c r="F100" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A100)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A100)</f>
         <v>0</v>
       </c>
       <c r="G100" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A100)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A100)</f>
         <v>0</v>
       </c>
       <c r="H100" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A100)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A100)</f>
         <v>0</v>
       </c>
       <c r="I100" s="8">
@@ -6310,7 +6150,7 @@
       <c r="N100" s="35"/>
     </row>
     <row r="101" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="67">
+      <c r="A101" s="58">
         <f t="shared" si="9"/>
         <v>1405</v>
       </c>
@@ -6319,27 +6159,27 @@
         <v>93</v>
       </c>
       <c r="C101" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A101)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A101)</f>
         <v>0</v>
       </c>
       <c r="D101" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A101)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A101)</f>
         <v>0</v>
       </c>
       <c r="E101" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A101)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A101)</f>
         <v>0</v>
       </c>
       <c r="F101" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A101)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A101)</f>
         <v>0</v>
       </c>
       <c r="G101" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A101)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A101)</f>
         <v>0</v>
       </c>
       <c r="H101" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A101)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A101)</f>
         <v>0</v>
       </c>
       <c r="I101" s="8">
@@ -6361,7 +6201,7 @@
       <c r="N101" s="35"/>
     </row>
     <row r="102" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="67">
+      <c r="A102" s="58">
         <f t="shared" si="9"/>
         <v>1420</v>
       </c>
@@ -6370,27 +6210,27 @@
         <v>94</v>
       </c>
       <c r="C102" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A102)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A102)</f>
         <v>0</v>
       </c>
       <c r="D102" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A102)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A102)</f>
         <v>0</v>
       </c>
       <c r="E102" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A102)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A102)</f>
         <v>0</v>
       </c>
       <c r="F102" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A102)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A102)</f>
         <v>0</v>
       </c>
       <c r="G102" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A102)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A102)</f>
         <v>0</v>
       </c>
       <c r="H102" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A102)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A102)</f>
         <v>0</v>
       </c>
       <c r="I102" s="8">
@@ -6412,7 +6252,7 @@
       <c r="N102" s="35"/>
     </row>
     <row r="103" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="67">
+      <c r="A103" s="58">
         <f t="shared" si="9"/>
         <v>1435</v>
       </c>
@@ -6421,27 +6261,27 @@
         <v>95</v>
       </c>
       <c r="C103" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A103)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A103)</f>
         <v>0</v>
       </c>
       <c r="D103" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A103)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A103)</f>
         <v>0</v>
       </c>
       <c r="E103" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A103)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A103)</f>
         <v>0</v>
       </c>
       <c r="F103" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A103)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A103)</f>
         <v>0</v>
       </c>
       <c r="G103" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A103)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A103)</f>
         <v>0</v>
       </c>
       <c r="H103" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A103)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A103)</f>
         <v>0</v>
       </c>
       <c r="I103" s="8">
@@ -6463,7 +6303,7 @@
       <c r="N103" s="35"/>
     </row>
     <row r="104" spans="1:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="67">
+      <c r="A104" s="58">
         <f t="shared" si="9"/>
         <v>1450</v>
       </c>
@@ -6472,27 +6312,27 @@
         <v>96</v>
       </c>
       <c r="C104" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,C$7,Dados!$A$1:$A$1994,$A104)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,C$7,Dados!$A$1:$A$1993,$A104)</f>
         <v>0</v>
       </c>
       <c r="D104" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,D$7,Dados!$A$1:$A$1994,$A104)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,D$7,Dados!$A$1:$A$1993,$A104)</f>
         <v>0</v>
       </c>
       <c r="E104" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,E$7,Dados!$A$1:$A$1994,$A104)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,E$7,Dados!$A$1:$A$1993,$A104)</f>
         <v>0</v>
       </c>
       <c r="F104" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,F$7,Dados!$A$1:$A$1994,$A104)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,F$7,Dados!$A$1:$A$1993,$A104)</f>
         <v>0</v>
       </c>
       <c r="G104" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,G$7,Dados!$A$1:$A$1994,$A104)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,G$7,Dados!$A$1:$A$1993,$A104)</f>
         <v>0</v>
       </c>
       <c r="H104" s="8">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$B$1:$B$1994,H$7,Dados!$A$1:$A$1994,$A104)</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$B$1:$B$1993,H$7,Dados!$A$1:$A$1993,$A104)</f>
         <v>0</v>
       </c>
       <c r="I104" s="8">
@@ -6596,19 +6436,19 @@
     <row r="1" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="G1" s="60" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
+      <c r="G1" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
     </row>
     <row r="2" spans="1:18" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="2"/>
@@ -6706,37 +6546,37 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="27.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43">
+      <c r="A9" s="41">
         <f>DATE(YEAR(RESUMO!A9),MONTH(RESUMO!A9),1)</f>
         <v>1</v>
       </c>
       <c r="B9" s="36"/>
       <c r="C9" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$131,Dados!$K$1:$K$131,Tp.Despesas!C$7,Dados!$A$1:$A$131,"&gt;="&amp;$A9,Dados!$A$1:$A$131,"&lt;="&amp;EOMONTH($A9,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$130,Dados!$K$1:$K$130,Tp.Despesas!C$7,Dados!$A$1:$A$130,"&gt;="&amp;$A9,Dados!$A$1:$A$130,"&lt;="&amp;EOMONTH($A9,0))</f>
         <v>0</v>
       </c>
       <c r="D9" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$131,Dados!$K$1:$K$131,Tp.Despesas!D$7,Dados!$A$1:$A$131,"&gt;="&amp;$A9,Dados!$A$1:$A$131,"&lt;="&amp;EOMONTH($A9,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$130,Dados!$K$1:$K$130,Tp.Despesas!D$7,Dados!$A$1:$A$130,"&gt;="&amp;$A9,Dados!$A$1:$A$130,"&lt;="&amp;EOMONTH($A9,0))</f>
         <v>0</v>
       </c>
       <c r="E9" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$131,Dados!$K$1:$K$131,Tp.Despesas!E$7,Dados!$A$1:$A$131,"&gt;="&amp;$A9,Dados!$A$1:$A$131,"&lt;="&amp;EOMONTH($A9,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$130,Dados!$K$1:$K$130,Tp.Despesas!E$7,Dados!$A$1:$A$130,"&gt;="&amp;$A9,Dados!$A$1:$A$130,"&lt;="&amp;EOMONTH($A9,0))</f>
         <v>0</v>
       </c>
       <c r="F9" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$131,Dados!$K$1:$K$131,Tp.Despesas!F$7,Dados!$A$1:$A$131,"&gt;="&amp;$A9,Dados!$A$1:$A$131,"&lt;="&amp;EOMONTH($A9,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$130,Dados!$K$1:$K$130,Tp.Despesas!F$7,Dados!$A$1:$A$130,"&gt;="&amp;$A9,Dados!$A$1:$A$130,"&lt;="&amp;EOMONTH($A9,0))</f>
         <v>0</v>
       </c>
       <c r="G9" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$131,Dados!$K$1:$K$131,Tp.Despesas!G$7,Dados!$A$1:$A$131,"&gt;="&amp;$A9,Dados!$A$1:$A$131,"&lt;="&amp;EOMONTH($A9,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$130,Dados!$K$1:$K$130,Tp.Despesas!G$7,Dados!$A$1:$A$130,"&gt;="&amp;$A9,Dados!$A$1:$A$130,"&lt;="&amp;EOMONTH($A9,0))</f>
         <v>0</v>
       </c>
       <c r="H9" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$131,Dados!$K$1:$K$131,Tp.Despesas!H$7,Dados!$A$1:$A$131,"&gt;="&amp;$A9,Dados!$A$1:$A$131,"&lt;="&amp;EOMONTH($A9,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$130,Dados!$K$1:$K$130,Tp.Despesas!H$7,Dados!$A$1:$A$130,"&gt;="&amp;$A9,Dados!$A$1:$A$130,"&lt;="&amp;EOMONTH($A9,0))</f>
         <v>0</v>
       </c>
       <c r="I9" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$131,Dados!$K$1:$K$131,Tp.Despesas!I$7,Dados!$A$1:$A$131,"&gt;="&amp;$A9,Dados!$A$1:$A$131,"&lt;="&amp;EOMONTH($A9,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$130,Dados!$K$1:$K$130,Tp.Despesas!I$7,Dados!$A$1:$A$130,"&gt;="&amp;$A9,Dados!$A$1:$A$130,"&lt;="&amp;EOMONTH($A9,0))</f>
         <v>0</v>
       </c>
       <c r="J9" s="19">
@@ -6745,37 +6585,37 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="43">
+      <c r="A10" s="41">
         <f>EOMONTH(A9,1)-DAY(EOMONTH(A9,1))+1</f>
         <v>32</v>
       </c>
       <c r="B10" s="37"/>
       <c r="C10" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A10,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A10,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A10,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A10,0))</f>
         <v>0</v>
       </c>
       <c r="D10" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A10,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A10,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A10,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A10,0))</f>
         <v>0</v>
       </c>
       <c r="E10" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A10,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A10,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A10,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A10,0))</f>
         <v>0</v>
       </c>
       <c r="F10" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A10,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A10,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A10,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A10,0))</f>
         <v>0</v>
       </c>
       <c r="G10" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A10,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A10,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A10,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A10,0))</f>
         <v>0</v>
       </c>
       <c r="H10" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A10,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A10,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A10,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A10,0))</f>
         <v>0</v>
       </c>
       <c r="I10" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A10,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A10,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A10,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A10,0))</f>
         <v>0</v>
       </c>
       <c r="J10" s="19">
@@ -6784,37 +6624,37 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="43">
+      <c r="A11" s="41">
         <f t="shared" ref="A11:A44" si="0">EOMONTH(A10,1)-DAY(EOMONTH(A10,1))+1</f>
         <v>61</v>
       </c>
       <c r="B11" s="37"/>
       <c r="C11" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A11,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A11,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A11,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A11,0))</f>
         <v>0</v>
       </c>
       <c r="D11" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A11,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A11,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A11,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A11,0))</f>
         <v>0</v>
       </c>
       <c r="E11" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A11,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A11,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A11,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A11,0))</f>
         <v>0</v>
       </c>
       <c r="F11" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A11,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A11,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A11,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A11,0))</f>
         <v>0</v>
       </c>
       <c r="G11" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A11,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A11,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A11,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A11,0))</f>
         <v>0</v>
       </c>
       <c r="H11" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A11,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A11,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A11,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A11,0))</f>
         <v>0</v>
       </c>
       <c r="I11" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A11,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A11,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A11,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A11,0))</f>
         <v>0</v>
       </c>
       <c r="J11" s="19">
@@ -6823,37 +6663,37 @@
       </c>
     </row>
     <row r="12" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="43">
+      <c r="A12" s="41">
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="B12" s="37"/>
       <c r="C12" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A12,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A12,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A12,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A12,0))</f>
         <v>0</v>
       </c>
       <c r="D12" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A12,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A12,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A12,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A12,0))</f>
         <v>0</v>
       </c>
       <c r="E12" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A12,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A12,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A12,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A12,0))</f>
         <v>0</v>
       </c>
       <c r="F12" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A12,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A12,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A12,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A12,0))</f>
         <v>0</v>
       </c>
       <c r="G12" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A12,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A12,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A12,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A12,0))</f>
         <v>0</v>
       </c>
       <c r="H12" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A12,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A12,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A12,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A12,0))</f>
         <v>0</v>
       </c>
       <c r="I12" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A12,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A12,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A12,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A12,0))</f>
         <v>0</v>
       </c>
       <c r="J12" s="19">
@@ -6862,37 +6702,37 @@
       </c>
     </row>
     <row r="13" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43">
+      <c r="A13" s="41">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
       <c r="B13" s="37"/>
       <c r="C13" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A13,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A13,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A13,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A13,0))</f>
         <v>0</v>
       </c>
       <c r="D13" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A13,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A13,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A13,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A13,0))</f>
         <v>0</v>
       </c>
       <c r="E13" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A13,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A13,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A13,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A13,0))</f>
         <v>0</v>
       </c>
       <c r="F13" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A13,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A13,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A13,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A13,0))</f>
         <v>0</v>
       </c>
       <c r="G13" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A13,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A13,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A13,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A13,0))</f>
         <v>0</v>
       </c>
       <c r="H13" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A13,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A13,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A13,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A13,0))</f>
         <v>0</v>
       </c>
       <c r="I13" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A13,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A13,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A13,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A13,0))</f>
         <v>0</v>
       </c>
       <c r="J13" s="19">
@@ -6901,37 +6741,37 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="43">
+      <c r="A14" s="41">
         <f t="shared" si="0"/>
         <v>153</v>
       </c>
       <c r="B14" s="37"/>
       <c r="C14" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A14,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A14,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A14,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A14,0))</f>
         <v>0</v>
       </c>
       <c r="D14" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A14,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A14,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A14,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A14,0))</f>
         <v>0</v>
       </c>
       <c r="E14" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A14,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A14,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A14,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A14,0))</f>
         <v>0</v>
       </c>
       <c r="F14" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A14,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A14,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A14,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A14,0))</f>
         <v>0</v>
       </c>
       <c r="G14" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A14,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A14,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A14,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A14,0))</f>
         <v>0</v>
       </c>
       <c r="H14" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A14,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A14,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A14,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A14,0))</f>
         <v>0</v>
       </c>
       <c r="I14" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A14,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A14,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A14,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A14,0))</f>
         <v>0</v>
       </c>
       <c r="J14" s="19">
@@ -6940,37 +6780,37 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="43">
+      <c r="A15" s="41">
         <f t="shared" si="0"/>
         <v>183</v>
       </c>
       <c r="B15" s="37"/>
       <c r="C15" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A15,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A15,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A15,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A15,0))</f>
         <v>0</v>
       </c>
       <c r="D15" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A15,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A15,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A15,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A15,0))</f>
         <v>0</v>
       </c>
       <c r="E15" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A15,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A15,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A15,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A15,0))</f>
         <v>0</v>
       </c>
       <c r="F15" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A15,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A15,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A15,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A15,0))</f>
         <v>0</v>
       </c>
       <c r="G15" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A15,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A15,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A15,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A15,0))</f>
         <v>0</v>
       </c>
       <c r="H15" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A15,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A15,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A15,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A15,0))</f>
         <v>0</v>
       </c>
       <c r="I15" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A15,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A15,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A15,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A15,0))</f>
         <v>0</v>
       </c>
       <c r="J15" s="19">
@@ -6979,37 +6819,37 @@
       </c>
     </row>
     <row r="16" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="43">
+      <c r="A16" s="41">
         <f t="shared" si="0"/>
         <v>214</v>
       </c>
       <c r="B16" s="37"/>
       <c r="C16" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A16,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A16,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A16,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A16,0))</f>
         <v>0</v>
       </c>
       <c r="D16" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A16,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A16,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A16,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A16,0))</f>
         <v>0</v>
       </c>
       <c r="E16" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A16,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A16,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A16,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A16,0))</f>
         <v>0</v>
       </c>
       <c r="F16" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A16,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A16,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A16,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A16,0))</f>
         <v>0</v>
       </c>
       <c r="G16" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A16,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A16,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A16,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A16,0))</f>
         <v>0</v>
       </c>
       <c r="H16" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A16,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A16,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A16,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A16,0))</f>
         <v>0</v>
       </c>
       <c r="I16" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A16,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A16,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A16,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A16,0))</f>
         <v>0</v>
       </c>
       <c r="J16" s="19">
@@ -7018,37 +6858,37 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43">
+      <c r="A17" s="41">
         <f t="shared" si="0"/>
         <v>245</v>
       </c>
       <c r="B17" s="37"/>
       <c r="C17" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A17,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A17,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A17,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A17,0))</f>
         <v>0</v>
       </c>
       <c r="D17" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A17,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A17,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A17,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A17,0))</f>
         <v>0</v>
       </c>
       <c r="E17" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A17,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A17,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A17,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A17,0))</f>
         <v>0</v>
       </c>
       <c r="F17" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A17,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A17,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A17,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A17,0))</f>
         <v>0</v>
       </c>
       <c r="G17" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A17,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A17,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A17,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A17,0))</f>
         <v>0</v>
       </c>
       <c r="H17" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A17,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A17,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A17,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A17,0))</f>
         <v>0</v>
       </c>
       <c r="I17" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A17,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A17,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A17,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A17,0))</f>
         <v>0</v>
       </c>
       <c r="J17" s="19">
@@ -7057,37 +6897,37 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="43">
+      <c r="A18" s="41">
         <f t="shared" si="0"/>
         <v>275</v>
       </c>
       <c r="B18" s="37"/>
       <c r="C18" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A18,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A18,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A18,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A18,0))</f>
         <v>0</v>
       </c>
       <c r="D18" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A18,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A18,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A18,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A18,0))</f>
         <v>0</v>
       </c>
       <c r="E18" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A18,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A18,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A18,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A18,0))</f>
         <v>0</v>
       </c>
       <c r="F18" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A18,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A18,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A18,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A18,0))</f>
         <v>0</v>
       </c>
       <c r="G18" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A18,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A18,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A18,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A18,0))</f>
         <v>0</v>
       </c>
       <c r="H18" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A18,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A18,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A18,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A18,0))</f>
         <v>0</v>
       </c>
       <c r="I18" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A18,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A18,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A18,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A18,0))</f>
         <v>0</v>
       </c>
       <c r="J18" s="19">
@@ -7096,37 +6936,37 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="43">
+      <c r="A19" s="41">
         <f t="shared" si="0"/>
         <v>306</v>
       </c>
       <c r="B19" s="37"/>
       <c r="C19" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A19,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A19,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A19,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A19,0))</f>
         <v>0</v>
       </c>
       <c r="D19" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A19,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A19,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A19,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A19,0))</f>
         <v>0</v>
       </c>
       <c r="E19" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A19,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A19,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A19,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A19,0))</f>
         <v>0</v>
       </c>
       <c r="F19" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A19,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A19,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A19,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A19,0))</f>
         <v>0</v>
       </c>
       <c r="G19" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A19,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A19,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A19,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A19,0))</f>
         <v>0</v>
       </c>
       <c r="H19" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A19,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A19,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A19,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A19,0))</f>
         <v>0</v>
       </c>
       <c r="I19" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A19,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A19,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A19,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A19,0))</f>
         <v>0</v>
       </c>
       <c r="J19" s="19">
@@ -7135,37 +6975,37 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="43">
+      <c r="A20" s="41">
         <f t="shared" si="0"/>
         <v>336</v>
       </c>
       <c r="B20" s="37"/>
       <c r="C20" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A20,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A20,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A20,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A20,0))</f>
         <v>0</v>
       </c>
       <c r="D20" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A20,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A20,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A20,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A20,0))</f>
         <v>0</v>
       </c>
       <c r="E20" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A20,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A20,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A20,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A20,0))</f>
         <v>0</v>
       </c>
       <c r="F20" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A20,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A20,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A20,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A20,0))</f>
         <v>0</v>
       </c>
       <c r="G20" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A20,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A20,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A20,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A20,0))</f>
         <v>0</v>
       </c>
       <c r="H20" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A20,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A20,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A20,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A20,0))</f>
         <v>0</v>
       </c>
       <c r="I20" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A20,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A20,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A20,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A20,0))</f>
         <v>0</v>
       </c>
       <c r="J20" s="19">
@@ -7174,37 +7014,37 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="43">
+      <c r="A21" s="41">
         <f t="shared" si="0"/>
         <v>367</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A21,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A21,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A21,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A21,0))</f>
         <v>0</v>
       </c>
       <c r="D21" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A21,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A21,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A21,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A21,0))</f>
         <v>0</v>
       </c>
       <c r="E21" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A21,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A21,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A21,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A21,0))</f>
         <v>0</v>
       </c>
       <c r="F21" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A21,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A21,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A21,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A21,0))</f>
         <v>0</v>
       </c>
       <c r="G21" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A21,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A21,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A21,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A21,0))</f>
         <v>0</v>
       </c>
       <c r="H21" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A21,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A21,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A21,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A21,0))</f>
         <v>0</v>
       </c>
       <c r="I21" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A21,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A21,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A21,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A21,0))</f>
         <v>0</v>
       </c>
       <c r="J21" s="18">
@@ -7213,37 +7053,37 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="43">
+      <c r="A22" s="41">
         <f t="shared" si="0"/>
         <v>398</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A22,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A22,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A22,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A22,0))</f>
         <v>0</v>
       </c>
       <c r="D22" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A22,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A22,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A22,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A22,0))</f>
         <v>0</v>
       </c>
       <c r="E22" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A22,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A22,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A22,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A22,0))</f>
         <v>0</v>
       </c>
       <c r="F22" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A22,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A22,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A22,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A22,0))</f>
         <v>0</v>
       </c>
       <c r="G22" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A22,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A22,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A22,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A22,0))</f>
         <v>0</v>
       </c>
       <c r="H22" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A22,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A22,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A22,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A22,0))</f>
         <v>0</v>
       </c>
       <c r="I22" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A22,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A22,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A22,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A22,0))</f>
         <v>0</v>
       </c>
       <c r="J22" s="19">
@@ -7252,37 +7092,37 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="43">
+      <c r="A23" s="41">
         <f t="shared" si="0"/>
         <v>426</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A23,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A23,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A23,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A23,0))</f>
         <v>0</v>
       </c>
       <c r="D23" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A23,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A23,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A23,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A23,0))</f>
         <v>0</v>
       </c>
       <c r="E23" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A23,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A23,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A23,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A23,0))</f>
         <v>0</v>
       </c>
       <c r="F23" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A23,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A23,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A23,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A23,0))</f>
         <v>0</v>
       </c>
       <c r="G23" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A23,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A23,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A23,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A23,0))</f>
         <v>0</v>
       </c>
       <c r="H23" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A23,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A23,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A23,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A23,0))</f>
         <v>0</v>
       </c>
       <c r="I23" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A23,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A23,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A23,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A23,0))</f>
         <v>0</v>
       </c>
       <c r="J23" s="19">
@@ -7291,37 +7131,37 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="43">
+      <c r="A24" s="41">
         <f t="shared" si="0"/>
         <v>457</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A24,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A24,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A24,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A24,0))</f>
         <v>0</v>
       </c>
       <c r="D24" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A24,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A24,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A24,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A24,0))</f>
         <v>0</v>
       </c>
       <c r="E24" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A24,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A24,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A24,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A24,0))</f>
         <v>0</v>
       </c>
       <c r="F24" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A24,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A24,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A24,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A24,0))</f>
         <v>0</v>
       </c>
       <c r="G24" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A24,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A24,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A24,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A24,0))</f>
         <v>0</v>
       </c>
       <c r="H24" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A24,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A24,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A24,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A24,0))</f>
         <v>0</v>
       </c>
       <c r="I24" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A24,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A24,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A24,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A24,0))</f>
         <v>0</v>
       </c>
       <c r="J24" s="19">
@@ -7330,37 +7170,37 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="43">
+      <c r="A25" s="41">
         <f t="shared" si="0"/>
         <v>487</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A25,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A25,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A25,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A25,0))</f>
         <v>0</v>
       </c>
       <c r="D25" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A25,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A25,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A25,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A25,0))</f>
         <v>0</v>
       </c>
       <c r="E25" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A25,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A25,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A25,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A25,0))</f>
         <v>0</v>
       </c>
       <c r="F25" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A25,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A25,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A25,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A25,0))</f>
         <v>0</v>
       </c>
       <c r="G25" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A25,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A25,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A25,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A25,0))</f>
         <v>0</v>
       </c>
       <c r="H25" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A25,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A25,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A25,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A25,0))</f>
         <v>0</v>
       </c>
       <c r="I25" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A25,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A25,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A25,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A25,0))</f>
         <v>0</v>
       </c>
       <c r="J25" s="19">
@@ -7369,37 +7209,37 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="43">
+      <c r="A26" s="41">
         <f t="shared" si="0"/>
         <v>518</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A26,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A26,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A26,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A26,0))</f>
         <v>0</v>
       </c>
       <c r="D26" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A26,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A26,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A26,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A26,0))</f>
         <v>0</v>
       </c>
       <c r="E26" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A26,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A26,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A26,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A26,0))</f>
         <v>0</v>
       </c>
       <c r="F26" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A26,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A26,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A26,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A26,0))</f>
         <v>0</v>
       </c>
       <c r="G26" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A26,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A26,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A26,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A26,0))</f>
         <v>0</v>
       </c>
       <c r="H26" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A26,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A26,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A26,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A26,0))</f>
         <v>0</v>
       </c>
       <c r="I26" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A26,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A26,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A26,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A26,0))</f>
         <v>0</v>
       </c>
       <c r="J26" s="19">
@@ -7408,37 +7248,37 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="43">
+      <c r="A27" s="41">
         <f t="shared" si="0"/>
         <v>548</v>
       </c>
       <c r="B27" s="31"/>
       <c r="C27" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A27,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A27,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A27,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A27,0))</f>
         <v>0</v>
       </c>
       <c r="D27" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A27,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A27,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A27,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A27,0))</f>
         <v>0</v>
       </c>
       <c r="E27" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A27,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A27,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A27,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A27,0))</f>
         <v>0</v>
       </c>
       <c r="F27" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A27,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A27,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A27,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A27,0))</f>
         <v>0</v>
       </c>
       <c r="G27" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A27,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A27,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A27,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A27,0))</f>
         <v>0</v>
       </c>
       <c r="H27" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A27,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A27,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A27,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A27,0))</f>
         <v>0</v>
       </c>
       <c r="I27" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A27,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A27,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A27,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A27,0))</f>
         <v>0</v>
       </c>
       <c r="J27" s="19">
@@ -7447,37 +7287,37 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="43">
+      <c r="A28" s="41">
         <f t="shared" si="0"/>
         <v>579</v>
       </c>
       <c r="B28" s="31"/>
       <c r="C28" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A28,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A28,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A28,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A28,0))</f>
         <v>0</v>
       </c>
       <c r="D28" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A28,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A28,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A28,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A28,0))</f>
         <v>0</v>
       </c>
       <c r="E28" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A28,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A28,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A28,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A28,0))</f>
         <v>0</v>
       </c>
       <c r="F28" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A28,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A28,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A28,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A28,0))</f>
         <v>0</v>
       </c>
       <c r="G28" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A28,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A28,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A28,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A28,0))</f>
         <v>0</v>
       </c>
       <c r="H28" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A28,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A28,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A28,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A28,0))</f>
         <v>0</v>
       </c>
       <c r="I28" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A28,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A28,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A28,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A28,0))</f>
         <v>0</v>
       </c>
       <c r="J28" s="19">
@@ -7486,37 +7326,37 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="43">
+      <c r="A29" s="41">
         <f t="shared" si="0"/>
         <v>610</v>
       </c>
       <c r="B29" s="31"/>
       <c r="C29" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A29,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A29,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A29,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A29,0))</f>
         <v>0</v>
       </c>
       <c r="D29" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A29,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A29,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A29,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A29,0))</f>
         <v>0</v>
       </c>
       <c r="E29" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A29,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A29,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A29,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A29,0))</f>
         <v>0</v>
       </c>
       <c r="F29" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A29,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A29,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A29,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A29,0))</f>
         <v>0</v>
       </c>
       <c r="G29" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A29,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A29,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A29,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A29,0))</f>
         <v>0</v>
       </c>
       <c r="H29" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A29,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A29,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A29,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A29,0))</f>
         <v>0</v>
       </c>
       <c r="I29" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A29,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A29,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A29,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A29,0))</f>
         <v>0</v>
       </c>
       <c r="J29" s="18">
@@ -7525,37 +7365,37 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="43">
+      <c r="A30" s="41">
         <f t="shared" si="0"/>
         <v>640</v>
       </c>
       <c r="B30" s="31"/>
       <c r="C30" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A30,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A30,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A30,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A30,0))</f>
         <v>0</v>
       </c>
       <c r="D30" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A30,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A30,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A30,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A30,0))</f>
         <v>0</v>
       </c>
       <c r="E30" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A30,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A30,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A30,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A30,0))</f>
         <v>0</v>
       </c>
       <c r="F30" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A30,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A30,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A30,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A30,0))</f>
         <v>0</v>
       </c>
       <c r="G30" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A30,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A30,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A30,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A30,0))</f>
         <v>0</v>
       </c>
       <c r="H30" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A30,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A30,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A30,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A30,0))</f>
         <v>0</v>
       </c>
       <c r="I30" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A30,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A30,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A30,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A30,0))</f>
         <v>0</v>
       </c>
       <c r="J30" s="19">
@@ -7564,37 +7404,37 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="43">
+      <c r="A31" s="41">
         <f t="shared" si="0"/>
         <v>671</v>
       </c>
       <c r="B31" s="31"/>
       <c r="C31" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A31,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A31,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A31,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A31,0))</f>
         <v>0</v>
       </c>
       <c r="D31" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A31,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A31,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A31,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A31,0))</f>
         <v>0</v>
       </c>
       <c r="E31" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A31,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A31,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A31,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A31,0))</f>
         <v>0</v>
       </c>
       <c r="F31" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A31,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A31,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A31,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A31,0))</f>
         <v>0</v>
       </c>
       <c r="G31" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A31,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A31,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A31,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A31,0))</f>
         <v>0</v>
       </c>
       <c r="H31" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A31,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A31,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A31,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A31,0))</f>
         <v>0</v>
       </c>
       <c r="I31" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A31,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A31,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A31,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A31,0))</f>
         <v>0</v>
       </c>
       <c r="J31" s="19">
@@ -7603,37 +7443,37 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="43">
+      <c r="A32" s="41">
         <f t="shared" si="0"/>
         <v>701</v>
       </c>
       <c r="B32" s="31"/>
       <c r="C32" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A32,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A32,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A32,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A32,0))</f>
         <v>0</v>
       </c>
       <c r="D32" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A32,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A32,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A32,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A32,0))</f>
         <v>0</v>
       </c>
       <c r="E32" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A32,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A32,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A32,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A32,0))</f>
         <v>0</v>
       </c>
       <c r="F32" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A32,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A32,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A32,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A32,0))</f>
         <v>0</v>
       </c>
       <c r="G32" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A32,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A32,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A32,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A32,0))</f>
         <v>0</v>
       </c>
       <c r="H32" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A32,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A32,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A32,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A32,0))</f>
         <v>0</v>
       </c>
       <c r="I32" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A32,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A32,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A32,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A32,0))</f>
         <v>0</v>
       </c>
       <c r="J32" s="19">
@@ -7642,37 +7482,37 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="43">
+      <c r="A33" s="41">
         <f t="shared" si="0"/>
         <v>732</v>
       </c>
       <c r="B33" s="31"/>
       <c r="C33" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A33,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A33,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A33,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A33,0))</f>
         <v>0</v>
       </c>
       <c r="D33" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A33,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A33,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A33,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A33,0))</f>
         <v>0</v>
       </c>
       <c r="E33" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A33,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A33,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A33,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A33,0))</f>
         <v>0</v>
       </c>
       <c r="F33" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A33,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A33,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A33,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A33,0))</f>
         <v>0</v>
       </c>
       <c r="G33" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A33,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A33,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A33,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A33,0))</f>
         <v>0</v>
       </c>
       <c r="H33" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A33,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A33,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A33,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A33,0))</f>
         <v>0</v>
       </c>
       <c r="I33" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A33,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A33,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A33,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A33,0))</f>
         <v>0</v>
       </c>
       <c r="J33" s="18">
@@ -7681,37 +7521,37 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="43">
+      <c r="A34" s="41">
         <f t="shared" si="0"/>
         <v>763</v>
       </c>
       <c r="B34" s="31"/>
       <c r="C34" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A34,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A34,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A34,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A34,0))</f>
         <v>0</v>
       </c>
       <c r="D34" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A34,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A34,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A34,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A34,0))</f>
         <v>0</v>
       </c>
       <c r="E34" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A34,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A34,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A34,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A34,0))</f>
         <v>0</v>
       </c>
       <c r="F34" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A34,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A34,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A34,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A34,0))</f>
         <v>0</v>
       </c>
       <c r="G34" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A34,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A34,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A34,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A34,0))</f>
         <v>0</v>
       </c>
       <c r="H34" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A34,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A34,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A34,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A34,0))</f>
         <v>0</v>
       </c>
       <c r="I34" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A34,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A34,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A34,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A34,0))</f>
         <v>0</v>
       </c>
       <c r="J34" s="19">
@@ -7720,37 +7560,37 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="43">
+      <c r="A35" s="41">
         <f t="shared" si="0"/>
         <v>791</v>
       </c>
       <c r="B35" s="31"/>
       <c r="C35" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A35,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A35,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A35,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A35,0))</f>
         <v>0</v>
       </c>
       <c r="D35" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A35,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A35,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A35,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A35,0))</f>
         <v>0</v>
       </c>
       <c r="E35" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A35,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A35,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A35,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A35,0))</f>
         <v>0</v>
       </c>
       <c r="F35" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A35,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A35,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A35,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A35,0))</f>
         <v>0</v>
       </c>
       <c r="G35" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A35,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A35,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A35,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A35,0))</f>
         <v>0</v>
       </c>
       <c r="H35" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A35,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A35,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A35,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A35,0))</f>
         <v>0</v>
       </c>
       <c r="I35" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A35,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A35,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A35,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A35,0))</f>
         <v>0</v>
       </c>
       <c r="J35" s="19">
@@ -7759,37 +7599,37 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="43">
+      <c r="A36" s="41">
         <f t="shared" si="0"/>
         <v>822</v>
       </c>
       <c r="B36" s="31"/>
       <c r="C36" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A36,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A36,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A36,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A36,0))</f>
         <v>0</v>
       </c>
       <c r="D36" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A36,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A36,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A36,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A36,0))</f>
         <v>0</v>
       </c>
       <c r="E36" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A36,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A36,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A36,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A36,0))</f>
         <v>0</v>
       </c>
       <c r="F36" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A36,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A36,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A36,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A36,0))</f>
         <v>0</v>
       </c>
       <c r="G36" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A36,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A36,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A36,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A36,0))</f>
         <v>0</v>
       </c>
       <c r="H36" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A36,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A36,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A36,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A36,0))</f>
         <v>0</v>
       </c>
       <c r="I36" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A36,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A36,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A36,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A36,0))</f>
         <v>0</v>
       </c>
       <c r="J36" s="19">
@@ -7798,37 +7638,37 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="43">
+      <c r="A37" s="41">
         <f t="shared" si="0"/>
         <v>852</v>
       </c>
       <c r="B37" s="31"/>
       <c r="C37" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A37,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A37,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A37,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A37,0))</f>
         <v>0</v>
       </c>
       <c r="D37" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A37,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A37,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A37,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A37,0))</f>
         <v>0</v>
       </c>
       <c r="E37" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A37,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A37,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A37,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A37,0))</f>
         <v>0</v>
       </c>
       <c r="F37" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A37,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A37,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A37,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A37,0))</f>
         <v>0</v>
       </c>
       <c r="G37" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A37,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A37,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A37,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A37,0))</f>
         <v>0</v>
       </c>
       <c r="H37" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A37,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A37,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A37,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A37,0))</f>
         <v>0</v>
       </c>
       <c r="I37" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A37,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A37,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A37,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A37,0))</f>
         <v>0</v>
       </c>
       <c r="J37" s="19">
@@ -7837,37 +7677,37 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="43">
+      <c r="A38" s="41">
         <f t="shared" si="0"/>
         <v>883</v>
       </c>
       <c r="B38" s="31"/>
       <c r="C38" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A38,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A38,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A38,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A38,0))</f>
         <v>0</v>
       </c>
       <c r="D38" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A38,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A38,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A38,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A38,0))</f>
         <v>0</v>
       </c>
       <c r="E38" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A38,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A38,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A38,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A38,0))</f>
         <v>0</v>
       </c>
       <c r="F38" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A38,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A38,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A38,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A38,0))</f>
         <v>0</v>
       </c>
       <c r="G38" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A38,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A38,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A38,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A38,0))</f>
         <v>0</v>
       </c>
       <c r="H38" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A38,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A38,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A38,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A38,0))</f>
         <v>0</v>
       </c>
       <c r="I38" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A38,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A38,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A38,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A38,0))</f>
         <v>0</v>
       </c>
       <c r="J38" s="19">
@@ -7876,37 +7716,37 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="43">
+      <c r="A39" s="41">
         <f t="shared" si="0"/>
         <v>913</v>
       </c>
       <c r="B39" s="31"/>
       <c r="C39" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A39,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A39,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A39,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A39,0))</f>
         <v>0</v>
       </c>
       <c r="D39" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A39,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A39,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A39,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A39,0))</f>
         <v>0</v>
       </c>
       <c r="E39" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A39,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A39,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A39,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A39,0))</f>
         <v>0</v>
       </c>
       <c r="F39" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A39,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A39,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A39,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A39,0))</f>
         <v>0</v>
       </c>
       <c r="G39" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A39,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A39,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A39,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A39,0))</f>
         <v>0</v>
       </c>
       <c r="H39" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A39,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A39,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A39,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A39,0))</f>
         <v>0</v>
       </c>
       <c r="I39" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A39,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A39,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A39,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A39,0))</f>
         <v>0</v>
       </c>
       <c r="J39" s="19">
@@ -7915,37 +7755,37 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="43">
+      <c r="A40" s="41">
         <f t="shared" si="0"/>
         <v>944</v>
       </c>
       <c r="B40" s="31"/>
       <c r="C40" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A40,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A40,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A40,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A40,0))</f>
         <v>0</v>
       </c>
       <c r="D40" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A40,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A40,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A40,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A40,0))</f>
         <v>0</v>
       </c>
       <c r="E40" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A40,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A40,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A40,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A40,0))</f>
         <v>0</v>
       </c>
       <c r="F40" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A40,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A40,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A40,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A40,0))</f>
         <v>0</v>
       </c>
       <c r="G40" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A40,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A40,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A40,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A40,0))</f>
         <v>0</v>
       </c>
       <c r="H40" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A40,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A40,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A40,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A40,0))</f>
         <v>0</v>
       </c>
       <c r="I40" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A40,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A40,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A40,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A40,0))</f>
         <v>0</v>
       </c>
       <c r="J40" s="19">
@@ -7954,37 +7794,37 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="43">
+      <c r="A41" s="41">
         <f t="shared" si="0"/>
         <v>975</v>
       </c>
       <c r="B41" s="31"/>
       <c r="C41" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A41,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A41,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A41,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A41,0))</f>
         <v>0</v>
       </c>
       <c r="D41" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A41,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A41,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A41,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A41,0))</f>
         <v>0</v>
       </c>
       <c r="E41" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A41,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A41,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A41,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A41,0))</f>
         <v>0</v>
       </c>
       <c r="F41" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A41,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A41,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A41,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A41,0))</f>
         <v>0</v>
       </c>
       <c r="G41" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A41,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A41,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A41,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A41,0))</f>
         <v>0</v>
       </c>
       <c r="H41" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A41,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A41,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A41,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A41,0))</f>
         <v>0</v>
       </c>
       <c r="I41" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A41,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A41,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A41,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A41,0))</f>
         <v>0</v>
       </c>
       <c r="J41" s="18">
@@ -7993,37 +7833,37 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="43">
+      <c r="A42" s="41">
         <f t="shared" si="0"/>
         <v>1005</v>
       </c>
       <c r="B42" s="31"/>
       <c r="C42" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A42,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A42,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A42,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A42,0))</f>
         <v>0</v>
       </c>
       <c r="D42" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A42,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A42,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A42,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A42,0))</f>
         <v>0</v>
       </c>
       <c r="E42" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A42,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A42,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A42,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A42,0))</f>
         <v>0</v>
       </c>
       <c r="F42" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A42,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A42,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A42,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A42,0))</f>
         <v>0</v>
       </c>
       <c r="G42" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A42,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A42,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A42,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A42,0))</f>
         <v>0</v>
       </c>
       <c r="H42" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A42,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A42,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A42,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A42,0))</f>
         <v>0</v>
       </c>
       <c r="I42" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A42,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A42,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A42,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A42,0))</f>
         <v>0</v>
       </c>
       <c r="J42" s="19">
@@ -8032,37 +7872,37 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="43">
+      <c r="A43" s="41">
         <f t="shared" si="0"/>
         <v>1036</v>
       </c>
       <c r="B43" s="31"/>
       <c r="C43" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A43,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A43,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A43,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A43,0))</f>
         <v>0</v>
       </c>
       <c r="D43" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A43,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A43,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A43,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A43,0))</f>
         <v>0</v>
       </c>
       <c r="E43" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A43,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A43,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A43,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A43,0))</f>
         <v>0</v>
       </c>
       <c r="F43" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A43,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A43,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A43,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A43,0))</f>
         <v>0</v>
       </c>
       <c r="G43" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A43,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A43,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A43,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A43,0))</f>
         <v>0</v>
       </c>
       <c r="H43" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A43,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A43,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A43,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A43,0))</f>
         <v>0</v>
       </c>
       <c r="I43" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A43,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A43,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A43,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A43,0))</f>
         <v>0</v>
       </c>
       <c r="J43" s="19">
@@ -8071,37 +7911,37 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="43">
+      <c r="A44" s="41">
         <f t="shared" si="0"/>
         <v>1066</v>
       </c>
       <c r="B44" s="31"/>
       <c r="C44" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!C$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A44,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A44,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!C$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A44,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A44,0))</f>
         <v>0</v>
       </c>
       <c r="D44" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!D$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A44,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A44,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!D$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A44,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A44,0))</f>
         <v>0</v>
       </c>
       <c r="E44" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!E$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A44,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A44,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!E$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A44,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A44,0))</f>
         <v>0</v>
       </c>
       <c r="F44" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!F$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A44,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A44,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!F$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A44,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A44,0))</f>
         <v>0</v>
       </c>
       <c r="G44" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!G$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A44,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A44,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!G$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A44,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A44,0))</f>
         <v>0</v>
       </c>
       <c r="H44" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!H$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A44,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A44,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!H$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A44,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A44,0))</f>
         <v>0</v>
       </c>
       <c r="I44" s="7">
-        <f>SUMIFS(Dados!$I$1:$I$1994,Dados!$K$1:$K$1994,Tp.Despesas!I$7,Dados!$J$1:$J$1994,"&gt;="&amp;$A44,Dados!$J$1:$J$1994,"&lt;="&amp;EOMONTH($A44,0))</f>
+        <f>SUMIFS(Dados!$I$1:$I$1993,Dados!$K$1:$K$1993,Tp.Despesas!I$7,Dados!$J$1:$J$1993,"&gt;="&amp;$A44,Dados!$J$1:$J$1993,"&lt;="&amp;EOMONTH($A44,0))</f>
         <v>0</v>
       </c>
       <c r="J44" s="19">
@@ -8110,10 +7950,10 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="33.950000000000003" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="62" t="s">
+      <c r="A45" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="B45" s="63"/>
+      <c r="B45" s="62"/>
       <c r="C45" s="26">
         <f t="shared" ref="C45:J45" si="2">SUM(C9:C44)</f>
         <v>0</v>
@@ -8148,8 +7988,8 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="64"/>
-      <c r="B46" s="65"/>
+      <c r="A46" s="63"/>
+      <c r="B46" s="64"/>
       <c r="C46" s="28" t="e">
         <f t="shared" ref="C46:J46" si="3">C45/$J$45</f>
         <v>#DIV/0!</v>
